--- a/input/timetable/Прикладная математика и информатика.xlsx
+++ b/input/timetable/Прикладная математика и информатика.xlsx
@@ -161,9 +161,6 @@
     <t>ФТД: Сети ЭВМ (лек), У704</t>
   </si>
   <si>
-    <t>Изобретательская деятельность (пр), У705</t>
-  </si>
-  <si>
     <t>Информационные технологии, п/г 1, У705</t>
   </si>
   <si>
@@ -356,9 +353,6 @@
     <t>//Иностранный язык в проф. сфере, п/г 2, У507</t>
   </si>
   <si>
-    <t>Изобретательская деятельность (лек), У705</t>
-  </si>
-  <si>
     <t>Геоинформационные технологии (лек), У506</t>
   </si>
   <si>
@@ -384,6 +378,12 @@
   </si>
   <si>
     <t>Методы машинного обучения (лек), У902</t>
+  </si>
+  <si>
+    <t>Изобретательская деятельность (лек), У902</t>
+  </si>
+  <si>
+    <t>Изобретательская деятельность (пр), У902</t>
   </si>
 </sst>
 </file>
@@ -1370,24 +1370,128 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1396,15 +1500,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1412,101 +1507,51 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1519,12 +1564,6 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1539,72 +1578,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1653,6 +1626,15 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1660,6 +1642,63 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1696,45 +1735,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2067,7 +2067,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -2083,14 +2083,14 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="63" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
@@ -2098,7 +2098,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
@@ -2127,12 +2127,12 @@
       <c r="A7" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="90" t="s">
+      <c r="C7" s="113" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="90"/>
+      <c r="D7" s="113"/>
       <c r="E7" s="40" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>7</v>
@@ -2142,12 +2142,12 @@
       <c r="A8" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="100" t="s">
-        <v>80</v>
-      </c>
-      <c r="D8" s="100"/>
-      <c r="E8" s="100"/>
-      <c r="F8" s="100"/>
+      <c r="C8" s="117" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="117"/>
+      <c r="E8" s="117"/>
+      <c r="F8" s="117"/>
     </row>
     <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="16" t="s">
@@ -2170,60 +2170,60 @@
       <c r="B10" s="23">
         <v>1</v>
       </c>
-      <c r="C10" s="101"/>
-      <c r="D10" s="70"/>
-      <c r="E10" s="79" t="s">
-        <v>52</v>
-      </c>
-      <c r="F10" s="80"/>
+      <c r="C10" s="118"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="110" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="120"/>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="24"/>
       <c r="B11" s="25">
         <v>2</v>
       </c>
-      <c r="C11" s="89" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" s="87"/>
-      <c r="E11" s="87" t="s">
-        <v>66</v>
-      </c>
-      <c r="F11" s="88"/>
+      <c r="C11" s="82" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="83"/>
+      <c r="E11" s="83" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="84"/>
     </row>
     <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="24"/>
       <c r="B12" s="25">
         <v>3</v>
       </c>
-      <c r="C12" s="97" t="s">
+      <c r="C12" s="103" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="98"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="99"/>
+      <c r="D12" s="104"/>
+      <c r="E12" s="104"/>
+      <c r="F12" s="105"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13" s="24"/>
       <c r="B13" s="25">
         <v>4</v>
       </c>
-      <c r="C13" s="91" t="s">
+      <c r="C13" s="97" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="92"/>
-      <c r="E13" s="92"/>
-      <c r="F13" s="93"/>
+      <c r="D13" s="98"/>
+      <c r="E13" s="98"/>
+      <c r="F13" s="99"/>
     </row>
     <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="26"/>
       <c r="B14" s="27">
         <v>5</v>
       </c>
-      <c r="C14" s="94"/>
-      <c r="D14" s="95"/>
-      <c r="E14" s="95"/>
-      <c r="F14" s="96"/>
+      <c r="C14" s="114"/>
+      <c r="D14" s="115"/>
+      <c r="E14" s="115"/>
+      <c r="F14" s="116"/>
     </row>
     <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="28" t="s">
@@ -2232,44 +2232,44 @@
       <c r="B15" s="29">
         <v>1</v>
       </c>
-      <c r="C15" s="102" t="s">
-        <v>95</v>
-      </c>
-      <c r="D15" s="103"/>
-      <c r="E15" s="103"/>
-      <c r="F15" s="104"/>
+      <c r="C15" s="67" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" s="68"/>
+      <c r="E15" s="68"/>
+      <c r="F15" s="69"/>
     </row>
     <row r="16" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="24"/>
       <c r="B16" s="25">
         <v>2</v>
       </c>
-      <c r="C16" s="105" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" s="106"/>
-      <c r="E16" s="106"/>
-      <c r="F16" s="107"/>
+      <c r="C16" s="70" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" s="71"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="72"/>
     </row>
     <row r="17" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="24"/>
       <c r="B17" s="25">
         <v>3</v>
       </c>
-      <c r="C17" s="75" t="s">
+      <c r="C17" s="125" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="76"/>
-      <c r="E17" s="76"/>
-      <c r="F17" s="77"/>
+      <c r="D17" s="126"/>
+      <c r="E17" s="126"/>
+      <c r="F17" s="127"/>
     </row>
     <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="30"/>
       <c r="B18" s="27"/>
-      <c r="C18" s="81"/>
-      <c r="D18" s="82"/>
-      <c r="E18" s="82"/>
-      <c r="F18" s="83"/>
+      <c r="C18" s="128"/>
+      <c r="D18" s="129"/>
+      <c r="E18" s="129"/>
+      <c r="F18" s="130"/>
     </row>
     <row r="19" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="28" t="s">
@@ -2278,50 +2278,50 @@
       <c r="B19" s="29">
         <v>2</v>
       </c>
-      <c r="C19" s="78" t="s">
-        <v>119</v>
-      </c>
-      <c r="D19" s="79"/>
-      <c r="E19" s="79"/>
-      <c r="F19" s="80"/>
+      <c r="C19" s="109" t="s">
+        <v>117</v>
+      </c>
+      <c r="D19" s="110"/>
+      <c r="E19" s="110"/>
+      <c r="F19" s="120"/>
     </row>
     <row r="20" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="24"/>
       <c r="B20" s="25">
         <v>3</v>
       </c>
-      <c r="C20" s="74" t="s">
-        <v>118</v>
-      </c>
-      <c r="D20" s="72"/>
-      <c r="E20" s="72"/>
-      <c r="F20" s="73"/>
+      <c r="C20" s="79" t="s">
+        <v>116</v>
+      </c>
+      <c r="D20" s="80"/>
+      <c r="E20" s="80"/>
+      <c r="F20" s="81"/>
     </row>
     <row r="21" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="24"/>
       <c r="B21" s="25">
         <v>4</v>
       </c>
-      <c r="C21" s="74" t="s">
-        <v>97</v>
-      </c>
-      <c r="D21" s="72"/>
-      <c r="E21" s="72"/>
-      <c r="F21" s="73"/>
+      <c r="C21" s="79" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" s="80"/>
+      <c r="E21" s="80"/>
+      <c r="F21" s="81"/>
     </row>
     <row r="22" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="30"/>
       <c r="B22" s="27">
         <v>5</v>
       </c>
-      <c r="C22" s="84" t="s">
+      <c r="C22" s="131" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" s="132"/>
+      <c r="E22" s="132" t="s">
         <v>104</v>
       </c>
-      <c r="D22" s="85"/>
-      <c r="E22" s="85" t="s">
-        <v>105</v>
-      </c>
-      <c r="F22" s="86"/>
+      <c r="F22" s="133"/>
     </row>
     <row r="23" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="28" t="s">
@@ -2330,48 +2330,48 @@
       <c r="B23" s="29">
         <v>1</v>
       </c>
-      <c r="C23" s="114" t="s">
-        <v>64</v>
-      </c>
-      <c r="D23" s="115"/>
-      <c r="E23" s="115"/>
-      <c r="F23" s="116"/>
+      <c r="C23" s="85" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" s="86"/>
+      <c r="E23" s="86"/>
+      <c r="F23" s="87"/>
     </row>
     <row r="24" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="24"/>
       <c r="B24" s="25">
         <v>2</v>
       </c>
-      <c r="C24" s="89" t="s">
-        <v>65</v>
-      </c>
-      <c r="D24" s="87"/>
-      <c r="E24" s="87"/>
-      <c r="F24" s="88"/>
+      <c r="C24" s="82" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="83"/>
+      <c r="E24" s="83"/>
+      <c r="F24" s="84"/>
     </row>
     <row r="25" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="24"/>
       <c r="B25" s="25">
         <v>3</v>
       </c>
-      <c r="C25" s="91" t="s">
+      <c r="C25" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="D25" s="92"/>
-      <c r="E25" s="92"/>
-      <c r="F25" s="93"/>
+      <c r="D25" s="98"/>
+      <c r="E25" s="98"/>
+      <c r="F25" s="99"/>
     </row>
     <row r="26" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="30"/>
       <c r="B26" s="27">
         <v>6</v>
       </c>
-      <c r="C26" s="120" t="s">
-        <v>51</v>
-      </c>
-      <c r="D26" s="121"/>
-      <c r="E26" s="121"/>
-      <c r="F26" s="122"/>
+      <c r="C26" s="91" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" s="92"/>
+      <c r="E26" s="92"/>
+      <c r="F26" s="93"/>
     </row>
     <row r="27" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="28" t="s">
@@ -2380,52 +2380,52 @@
       <c r="B27" s="29">
         <v>1</v>
       </c>
-      <c r="C27" s="78" t="s">
-        <v>47</v>
-      </c>
-      <c r="D27" s="79"/>
-      <c r="E27" s="70"/>
-      <c r="F27" s="71"/>
+      <c r="C27" s="109" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="110"/>
+      <c r="E27" s="119"/>
+      <c r="F27" s="124"/>
     </row>
     <row r="28" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="31"/>
       <c r="B28" s="25">
         <v>2</v>
       </c>
-      <c r="C28" s="132" t="s">
+      <c r="C28" s="111" t="s">
         <v>37</v>
       </c>
-      <c r="D28" s="133"/>
-      <c r="E28" s="72" t="s">
-        <v>48</v>
-      </c>
-      <c r="F28" s="73"/>
+      <c r="D28" s="112"/>
+      <c r="E28" s="80" t="s">
+        <v>47</v>
+      </c>
+      <c r="F28" s="81"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29" s="31"/>
       <c r="B29" s="25">
         <v>3</v>
       </c>
-      <c r="C29" s="89" t="s">
-        <v>49</v>
-      </c>
-      <c r="D29" s="87"/>
-      <c r="E29" s="87" t="s">
-        <v>94</v>
-      </c>
-      <c r="F29" s="88"/>
+      <c r="C29" s="82" t="s">
+        <v>48</v>
+      </c>
+      <c r="D29" s="83"/>
+      <c r="E29" s="83" t="s">
+        <v>93</v>
+      </c>
+      <c r="F29" s="84"/>
     </row>
     <row r="30" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="32"/>
       <c r="B30" s="27">
         <v>4</v>
       </c>
-      <c r="C30" s="123" t="s">
+      <c r="C30" s="94" t="s">
         <v>28</v>
       </c>
-      <c r="D30" s="124"/>
-      <c r="E30" s="124"/>
-      <c r="F30" s="125"/>
+      <c r="D30" s="95"/>
+      <c r="E30" s="95"/>
+      <c r="F30" s="96"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" s="33" t="s">
@@ -2434,83 +2434,83 @@
       <c r="B31" s="23">
         <v>2</v>
       </c>
-      <c r="C31" s="117" t="s">
-        <v>59</v>
-      </c>
-      <c r="D31" s="118"/>
-      <c r="E31" s="118"/>
-      <c r="F31" s="119"/>
+      <c r="C31" s="88" t="s">
+        <v>58</v>
+      </c>
+      <c r="D31" s="89"/>
+      <c r="E31" s="89"/>
+      <c r="F31" s="90"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" s="34"/>
       <c r="B32" s="25">
         <v>3</v>
       </c>
-      <c r="C32" s="126"/>
-      <c r="D32" s="127"/>
-      <c r="E32" s="127"/>
-      <c r="F32" s="128"/>
+      <c r="C32" s="100"/>
+      <c r="D32" s="101"/>
+      <c r="E32" s="101"/>
+      <c r="F32" s="102"/>
     </row>
     <row r="33" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="35"/>
       <c r="B33" s="36">
         <v>4</v>
       </c>
-      <c r="C33" s="97"/>
-      <c r="D33" s="98"/>
-      <c r="E33" s="98"/>
-      <c r="F33" s="99"/>
+      <c r="C33" s="103"/>
+      <c r="D33" s="104"/>
+      <c r="E33" s="104"/>
+      <c r="F33" s="105"/>
     </row>
     <row r="34" spans="1:6" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="41"/>
       <c r="B34" s="42"/>
-      <c r="C34" s="111"/>
-      <c r="D34" s="112"/>
-      <c r="E34" s="112"/>
-      <c r="F34" s="113"/>
+      <c r="C34" s="76"/>
+      <c r="D34" s="77"/>
+      <c r="E34" s="77"/>
+      <c r="F34" s="78"/>
     </row>
     <row r="35" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="37"/>
       <c r="B35" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="C35" s="129" t="s">
-        <v>72</v>
-      </c>
-      <c r="D35" s="130"/>
-      <c r="E35" s="130"/>
-      <c r="F35" s="131"/>
+      <c r="C35" s="106" t="s">
+        <v>71</v>
+      </c>
+      <c r="D35" s="107"/>
+      <c r="E35" s="107"/>
+      <c r="F35" s="108"/>
     </row>
     <row r="36" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="61"/>
       <c r="B36" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="C36" s="67" t="s">
-        <v>73</v>
-      </c>
-      <c r="D36" s="68"/>
-      <c r="E36" s="68"/>
-      <c r="F36" s="69"/>
+      <c r="C36" s="121" t="s">
+        <v>72</v>
+      </c>
+      <c r="D36" s="122"/>
+      <c r="E36" s="122"/>
+      <c r="F36" s="123"/>
     </row>
     <row r="37" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A37" s="38"/>
       <c r="B37" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="C37" s="108" t="s">
+      <c r="C37" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="D37" s="109"/>
-      <c r="E37" s="109"/>
-      <c r="F37" s="110"/>
+      <c r="D37" s="74"/>
+      <c r="E37" s="74"/>
+      <c r="F37" s="75"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A38" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.4">
@@ -2523,6 +2523,26 @@
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C37:F37"/>
@@ -2539,26 +2559,6 @@
     <mergeCell ref="C35:F35"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="C29:D29"/>
   </mergeCells>
   <conditionalFormatting sqref="C8">
     <cfRule type="expression" priority="1">
@@ -2603,7 +2603,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -2619,14 +2619,14 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="63" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
@@ -2634,7 +2634,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
@@ -2663,12 +2663,12 @@
       <c r="A7" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="90" t="s">
+      <c r="C7" s="113" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="90"/>
+      <c r="D7" s="113"/>
       <c r="E7" s="44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>7</v>
@@ -2678,12 +2678,12 @@
       <c r="A8" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="100" t="s">
-        <v>80</v>
-      </c>
-      <c r="D8" s="100"/>
-      <c r="E8" s="100"/>
-      <c r="F8" s="100"/>
+      <c r="C8" s="117" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="117"/>
+      <c r="E8" s="117"/>
+      <c r="F8" s="117"/>
     </row>
     <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="16" t="s">
@@ -2706,12 +2706,12 @@
       <c r="B10" s="29">
         <v>1</v>
       </c>
-      <c r="C10" s="139"/>
+      <c r="C10" s="160"/>
       <c r="D10" s="140"/>
-      <c r="E10" s="141" t="s">
-        <v>66</v>
-      </c>
-      <c r="F10" s="142"/>
+      <c r="E10" s="139" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="161"/>
       <c r="G10" s="64"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
@@ -2719,36 +2719,36 @@
       <c r="B11" s="25">
         <v>2</v>
       </c>
-      <c r="C11" s="75" t="s">
-        <v>98</v>
-      </c>
-      <c r="D11" s="76"/>
-      <c r="E11" s="76"/>
-      <c r="F11" s="77"/>
+      <c r="C11" s="125" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" s="126"/>
+      <c r="E11" s="126"/>
+      <c r="F11" s="127"/>
     </row>
     <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="24"/>
       <c r="B12" s="25">
         <v>3</v>
       </c>
-      <c r="C12" s="75" t="s">
-        <v>99</v>
-      </c>
-      <c r="D12" s="76"/>
-      <c r="E12" s="76"/>
-      <c r="F12" s="77"/>
+      <c r="C12" s="125" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" s="126"/>
+      <c r="E12" s="126"/>
+      <c r="F12" s="127"/>
     </row>
     <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="26"/>
       <c r="B13" s="59" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" s="136" t="s">
-        <v>62</v>
-      </c>
-      <c r="D13" s="137"/>
-      <c r="E13" s="137"/>
-      <c r="F13" s="138"/>
+        <v>67</v>
+      </c>
+      <c r="C13" s="157" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="158"/>
+      <c r="E13" s="158"/>
+      <c r="F13" s="159"/>
     </row>
     <row r="14" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="28" t="s">
@@ -2757,44 +2757,44 @@
       <c r="B14" s="29">
         <v>3</v>
       </c>
-      <c r="C14" s="143" t="s">
-        <v>69</v>
-      </c>
-      <c r="D14" s="144"/>
-      <c r="E14" s="144"/>
-      <c r="F14" s="145"/>
+      <c r="C14" s="162" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="163"/>
+      <c r="E14" s="163"/>
+      <c r="F14" s="164"/>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="24"/>
       <c r="B15" s="25">
         <v>4</v>
       </c>
-      <c r="C15" s="74" t="s">
-        <v>70</v>
-      </c>
-      <c r="D15" s="72"/>
-      <c r="E15" s="72"/>
-      <c r="F15" s="73"/>
+      <c r="C15" s="79" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="80"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="81"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16" s="24"/>
       <c r="B16" s="25">
         <v>5</v>
       </c>
-      <c r="C16" s="149"/>
-      <c r="D16" s="150"/>
-      <c r="E16" s="150"/>
-      <c r="F16" s="151"/>
+      <c r="C16" s="168"/>
+      <c r="D16" s="169"/>
+      <c r="E16" s="169"/>
+      <c r="F16" s="170"/>
     </row>
     <row r="17" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="30"/>
       <c r="B17" s="27">
         <v>6</v>
       </c>
-      <c r="C17" s="81"/>
-      <c r="D17" s="82"/>
-      <c r="E17" s="82"/>
-      <c r="F17" s="83"/>
+      <c r="C17" s="128"/>
+      <c r="D17" s="129"/>
+      <c r="E17" s="129"/>
+      <c r="F17" s="130"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A18" s="28" t="s">
@@ -2803,46 +2803,46 @@
       <c r="B18" s="29">
         <v>1</v>
       </c>
-      <c r="C18" s="146" t="s">
-        <v>57</v>
-      </c>
-      <c r="D18" s="147"/>
-      <c r="E18" s="147"/>
-      <c r="F18" s="148"/>
+      <c r="C18" s="165" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="166"/>
+      <c r="E18" s="166"/>
+      <c r="F18" s="167"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19" s="24"/>
       <c r="B19" s="25">
         <v>2</v>
       </c>
-      <c r="C19" s="74" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" s="72"/>
-      <c r="E19" s="72"/>
-      <c r="F19" s="73"/>
+      <c r="C19" s="79" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="80"/>
+      <c r="E19" s="80"/>
+      <c r="F19" s="81"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A20" s="24"/>
       <c r="B20" s="25">
         <v>3</v>
       </c>
-      <c r="C20" s="91" t="s">
-        <v>100</v>
-      </c>
-      <c r="D20" s="92"/>
-      <c r="E20" s="92"/>
-      <c r="F20" s="93"/>
+      <c r="C20" s="97" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" s="98"/>
+      <c r="E20" s="98"/>
+      <c r="F20" s="99"/>
     </row>
     <row r="21" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="30"/>
       <c r="B21" s="27">
         <v>4</v>
       </c>
-      <c r="C21" s="81"/>
-      <c r="D21" s="82"/>
-      <c r="E21" s="82"/>
-      <c r="F21" s="83"/>
+      <c r="C21" s="128"/>
+      <c r="D21" s="129"/>
+      <c r="E21" s="129"/>
+      <c r="F21" s="130"/>
     </row>
     <row r="22" spans="1:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="28" t="s">
@@ -2851,50 +2851,50 @@
       <c r="B22" s="29">
         <v>1</v>
       </c>
-      <c r="C22" s="169" t="s">
-        <v>55</v>
-      </c>
-      <c r="D22" s="141"/>
+      <c r="C22" s="138" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="139"/>
       <c r="E22" s="140"/>
-      <c r="F22" s="170"/>
+      <c r="F22" s="141"/>
     </row>
     <row r="23" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="24"/>
       <c r="B23" s="25">
         <v>2</v>
       </c>
-      <c r="C23" s="165" t="s">
+      <c r="C23" s="134" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="166"/>
-      <c r="E23" s="167" t="s">
-        <v>56</v>
-      </c>
-      <c r="F23" s="168"/>
+      <c r="D23" s="135"/>
+      <c r="E23" s="136" t="s">
+        <v>55</v>
+      </c>
+      <c r="F23" s="137"/>
     </row>
     <row r="24" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="24"/>
       <c r="B24" s="25">
         <v>3</v>
       </c>
-      <c r="C24" s="74" t="s">
-        <v>71</v>
-      </c>
-      <c r="D24" s="72"/>
-      <c r="E24" s="72"/>
-      <c r="F24" s="73"/>
+      <c r="C24" s="79" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="80"/>
+      <c r="E24" s="80"/>
+      <c r="F24" s="81"/>
     </row>
     <row r="25" spans="1:11" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="30"/>
       <c r="B25" s="59" t="s">
-        <v>68</v>
-      </c>
-      <c r="C25" s="136" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" s="137"/>
-      <c r="E25" s="137"/>
-      <c r="F25" s="138"/>
+        <v>67</v>
+      </c>
+      <c r="C25" s="157" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="158"/>
+      <c r="E25" s="158"/>
+      <c r="F25" s="159"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A26" s="28" t="s">
@@ -2903,26 +2903,26 @@
       <c r="B26" s="29">
         <v>2</v>
       </c>
-      <c r="C26" s="129" t="s">
+      <c r="C26" s="106" t="s">
+        <v>105</v>
+      </c>
+      <c r="D26" s="155"/>
+      <c r="E26" s="156" t="s">
         <v>106</v>
       </c>
-      <c r="D26" s="134"/>
-      <c r="E26" s="135" t="s">
-        <v>107</v>
-      </c>
-      <c r="F26" s="131"/>
+      <c r="F26" s="108"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A27" s="31"/>
       <c r="B27" s="25">
         <v>3</v>
       </c>
-      <c r="C27" s="74" t="s">
+      <c r="C27" s="79" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="72"/>
-      <c r="E27" s="72"/>
-      <c r="F27" s="73"/>
+      <c r="D27" s="80"/>
+      <c r="E27" s="80"/>
+      <c r="F27" s="81"/>
       <c r="K27" s="45"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.4">
@@ -2930,20 +2930,20 @@
       <c r="B28" s="25">
         <v>4</v>
       </c>
-      <c r="C28" s="74" t="s">
+      <c r="C28" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="72"/>
-      <c r="E28" s="72"/>
-      <c r="F28" s="73"/>
+      <c r="D28" s="80"/>
+      <c r="E28" s="80"/>
+      <c r="F28" s="81"/>
     </row>
     <row r="29" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="32"/>
       <c r="B29" s="27"/>
-      <c r="C29" s="153"/>
-      <c r="D29" s="154"/>
-      <c r="E29" s="154"/>
-      <c r="F29" s="155"/>
+      <c r="C29" s="143"/>
+      <c r="D29" s="144"/>
+      <c r="E29" s="144"/>
+      <c r="F29" s="145"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A30" s="46" t="s">
@@ -2952,83 +2952,83 @@
       <c r="B30" s="29">
         <v>1</v>
       </c>
-      <c r="C30" s="117" t="s">
-        <v>59</v>
-      </c>
-      <c r="D30" s="118"/>
-      <c r="E30" s="118"/>
-      <c r="F30" s="119"/>
+      <c r="C30" s="88" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="89"/>
+      <c r="E30" s="89"/>
+      <c r="F30" s="90"/>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="34"/>
       <c r="B31" s="25">
         <v>2</v>
       </c>
-      <c r="C31" s="156"/>
-      <c r="D31" s="157"/>
-      <c r="E31" s="157"/>
-      <c r="F31" s="158"/>
+      <c r="C31" s="146"/>
+      <c r="D31" s="147"/>
+      <c r="E31" s="147"/>
+      <c r="F31" s="148"/>
     </row>
     <row r="32" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A32" s="47"/>
       <c r="B32" s="27">
         <v>3</v>
       </c>
-      <c r="C32" s="159"/>
-      <c r="D32" s="160"/>
-      <c r="E32" s="160"/>
-      <c r="F32" s="161"/>
+      <c r="C32" s="149"/>
+      <c r="D32" s="150"/>
+      <c r="E32" s="150"/>
+      <c r="F32" s="151"/>
     </row>
     <row r="33" spans="1:6" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="48"/>
       <c r="B33" s="49"/>
-      <c r="C33" s="162"/>
-      <c r="D33" s="163"/>
-      <c r="E33" s="163"/>
-      <c r="F33" s="164"/>
+      <c r="C33" s="152"/>
+      <c r="D33" s="153"/>
+      <c r="E33" s="153"/>
+      <c r="F33" s="154"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A34" s="37"/>
       <c r="B34" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="129" t="s">
-        <v>74</v>
-      </c>
-      <c r="D34" s="130"/>
-      <c r="E34" s="130"/>
-      <c r="F34" s="131"/>
+      <c r="C34" s="106" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34" s="107"/>
+      <c r="E34" s="107"/>
+      <c r="F34" s="108"/>
     </row>
     <row r="35" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A35" s="38"/>
       <c r="B35" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="C35" s="108" t="s">
-        <v>83</v>
-      </c>
-      <c r="D35" s="109"/>
-      <c r="E35" s="109"/>
-      <c r="F35" s="110"/>
+      <c r="C35" s="73" t="s">
+        <v>82</v>
+      </c>
+      <c r="D35" s="74"/>
+      <c r="E35" s="74"/>
+      <c r="F35" s="75"/>
     </row>
     <row r="36" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="57" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B36" s="58"/>
-      <c r="C36" s="152" t="s">
-        <v>67</v>
-      </c>
-      <c r="D36" s="152"/>
-      <c r="E36" s="152"/>
-      <c r="F36" s="152"/>
+      <c r="C36" s="142" t="s">
+        <v>66</v>
+      </c>
+      <c r="D36" s="142"/>
+      <c r="E36" s="142"/>
+      <c r="F36" s="142"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.4">
@@ -3041,23 +3041,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C28:F28"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="C7:D7"/>
@@ -3074,6 +3057,23 @@
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
   </mergeCells>
   <conditionalFormatting sqref="C8">
     <cfRule type="expression" priority="1">
@@ -3121,7 +3121,7 @@
     </row>
     <row r="2" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3145,14 +3145,14 @@
     </row>
     <row r="4" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
@@ -3192,10 +3192,10 @@
         <v>16</v>
       </c>
       <c r="B7" s="2"/>
-      <c r="C7" s="90" t="s">
+      <c r="C7" s="113" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="90"/>
+      <c r="D7" s="113"/>
       <c r="E7" s="40" t="s">
         <v>43</v>
       </c>
@@ -3208,12 +3208,12 @@
         <v>26</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="100" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" s="100"/>
-      <c r="E8" s="100"/>
-      <c r="F8" s="100"/>
+      <c r="C8" s="117" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" s="117"/>
+      <c r="E8" s="117"/>
+      <c r="F8" s="117"/>
     </row>
     <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="16" t="s">
@@ -3236,58 +3236,58 @@
       <c r="B10" s="23">
         <v>1</v>
       </c>
-      <c r="C10" s="114" t="s">
-        <v>113</v>
-      </c>
-      <c r="D10" s="115"/>
-      <c r="E10" s="115"/>
-      <c r="F10" s="116"/>
+      <c r="C10" s="85" t="s">
+        <v>111</v>
+      </c>
+      <c r="D10" s="86"/>
+      <c r="E10" s="86"/>
+      <c r="F10" s="87"/>
     </row>
     <row r="11" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A11" s="24"/>
       <c r="B11" s="25">
         <v>2</v>
       </c>
-      <c r="C11" s="67" t="s">
-        <v>102</v>
-      </c>
-      <c r="D11" s="68"/>
-      <c r="E11" s="68"/>
-      <c r="F11" s="69"/>
+      <c r="C11" s="121" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" s="122"/>
+      <c r="E11" s="122"/>
+      <c r="F11" s="123"/>
     </row>
     <row r="12" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A12" s="24"/>
       <c r="B12" s="25">
         <v>3</v>
       </c>
-      <c r="C12" s="91" t="s">
-        <v>88</v>
-      </c>
-      <c r="D12" s="92"/>
-      <c r="E12" s="92"/>
-      <c r="F12" s="93"/>
+      <c r="C12" s="97" t="s">
+        <v>87</v>
+      </c>
+      <c r="D12" s="98"/>
+      <c r="E12" s="98"/>
+      <c r="F12" s="99"/>
     </row>
     <row r="13" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="24"/>
       <c r="B13" s="25">
         <v>4</v>
       </c>
-      <c r="C13" s="171" t="s">
+      <c r="C13" s="190" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="172"/>
-      <c r="E13" s="172"/>
-      <c r="F13" s="173"/>
+      <c r="D13" s="191"/>
+      <c r="E13" s="191"/>
+      <c r="F13" s="192"/>
     </row>
     <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="26"/>
       <c r="B14" s="27">
         <v>5</v>
       </c>
-      <c r="C14" s="174"/>
-      <c r="D14" s="175"/>
-      <c r="E14" s="175"/>
-      <c r="F14" s="176"/>
+      <c r="C14" s="199"/>
+      <c r="D14" s="200"/>
+      <c r="E14" s="200"/>
+      <c r="F14" s="201"/>
     </row>
     <row r="15" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A15" s="28" t="s">
@@ -3296,44 +3296,44 @@
       <c r="B15" s="29">
         <v>4</v>
       </c>
-      <c r="C15" s="91" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" s="92"/>
-      <c r="E15" s="92"/>
-      <c r="F15" s="93"/>
+      <c r="C15" s="97" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" s="98"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="99"/>
     </row>
     <row r="16" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A16" s="24"/>
       <c r="B16" s="25">
         <v>5</v>
       </c>
-      <c r="C16" s="171" t="s">
-        <v>84</v>
-      </c>
-      <c r="D16" s="172"/>
-      <c r="E16" s="172"/>
-      <c r="F16" s="173"/>
+      <c r="C16" s="190" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="191"/>
+      <c r="E16" s="191"/>
+      <c r="F16" s="192"/>
     </row>
     <row r="17" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="24"/>
       <c r="B17" s="25">
         <v>6</v>
       </c>
-      <c r="C17" s="105" t="s">
-        <v>85</v>
-      </c>
-      <c r="D17" s="106"/>
-      <c r="E17" s="106"/>
-      <c r="F17" s="107"/>
+      <c r="C17" s="70" t="s">
+        <v>84</v>
+      </c>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="72"/>
     </row>
     <row r="18" spans="1:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="30"/>
       <c r="B18" s="27"/>
-      <c r="C18" s="177"/>
-      <c r="D18" s="178"/>
-      <c r="E18" s="178"/>
-      <c r="F18" s="179"/>
+      <c r="C18" s="202"/>
+      <c r="D18" s="203"/>
+      <c r="E18" s="203"/>
+      <c r="F18" s="204"/>
       <c r="L18" s="60"/>
     </row>
     <row r="19" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -3343,46 +3343,46 @@
       <c r="B19" s="29">
         <v>1</v>
       </c>
-      <c r="C19" s="169" t="s">
-        <v>114</v>
-      </c>
-      <c r="D19" s="141"/>
-      <c r="E19" s="141"/>
-      <c r="F19" s="142"/>
+      <c r="C19" s="138" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" s="139"/>
+      <c r="E19" s="139"/>
+      <c r="F19" s="161"/>
     </row>
     <row r="20" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="24"/>
       <c r="B20" s="25">
         <v>2</v>
       </c>
-      <c r="C20" s="180" t="s">
-        <v>115</v>
-      </c>
-      <c r="D20" s="181"/>
-      <c r="E20" s="181"/>
-      <c r="F20" s="182"/>
+      <c r="C20" s="171" t="s">
+        <v>113</v>
+      </c>
+      <c r="D20" s="172"/>
+      <c r="E20" s="172"/>
+      <c r="F20" s="173"/>
     </row>
     <row r="21" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="24"/>
       <c r="B21" s="25">
         <v>3</v>
       </c>
-      <c r="C21" s="180" t="s">
-        <v>116</v>
-      </c>
-      <c r="D21" s="181"/>
-      <c r="E21" s="181"/>
-      <c r="F21" s="182"/>
+      <c r="C21" s="171" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" s="172"/>
+      <c r="E21" s="172"/>
+      <c r="F21" s="173"/>
     </row>
     <row r="22" spans="1:12" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="30"/>
       <c r="B22" s="27">
         <v>4</v>
       </c>
-      <c r="C22" s="183"/>
-      <c r="D22" s="184"/>
-      <c r="E22" s="184"/>
-      <c r="F22" s="185"/>
+      <c r="C22" s="174"/>
+      <c r="D22" s="175"/>
+      <c r="E22" s="175"/>
+      <c r="F22" s="176"/>
     </row>
     <row r="23" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A23" s="28" t="s">
@@ -3391,92 +3391,92 @@
       <c r="B23" s="29">
         <v>2</v>
       </c>
-      <c r="C23" s="114" t="s">
-        <v>120</v>
-      </c>
-      <c r="D23" s="115"/>
-      <c r="E23" s="115"/>
-      <c r="F23" s="116"/>
+      <c r="C23" s="85" t="s">
+        <v>118</v>
+      </c>
+      <c r="D23" s="86"/>
+      <c r="E23" s="86"/>
+      <c r="F23" s="87"/>
     </row>
     <row r="24" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A24" s="24"/>
       <c r="B24" s="25">
         <v>3</v>
       </c>
-      <c r="C24" s="67" t="s">
-        <v>86</v>
-      </c>
-      <c r="D24" s="68"/>
-      <c r="E24" s="68"/>
-      <c r="F24" s="69"/>
+      <c r="C24" s="121" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" s="122"/>
+      <c r="E24" s="122"/>
+      <c r="F24" s="123"/>
     </row>
     <row r="25" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A25" s="24"/>
       <c r="B25" s="25">
         <v>4</v>
       </c>
-      <c r="C25" s="180"/>
-      <c r="D25" s="181"/>
-      <c r="E25" s="181"/>
-      <c r="F25" s="182"/>
+      <c r="C25" s="171"/>
+      <c r="D25" s="172"/>
+      <c r="E25" s="172"/>
+      <c r="F25" s="173"/>
     </row>
     <row r="26" spans="1:12" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="30"/>
       <c r="B26" s="27">
         <v>5</v>
       </c>
-      <c r="C26" s="189"/>
-      <c r="D26" s="190"/>
-      <c r="E26" s="190"/>
-      <c r="F26" s="191"/>
+      <c r="C26" s="180"/>
+      <c r="D26" s="181"/>
+      <c r="E26" s="181"/>
+      <c r="F26" s="182"/>
     </row>
     <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="28" t="s">
         <v>24</v>
       </c>
       <c r="B27" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" s="187" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="196" t="s">
-        <v>62</v>
-      </c>
-      <c r="D27" s="197"/>
-      <c r="E27" s="197"/>
-      <c r="F27" s="198"/>
+      <c r="D27" s="188"/>
+      <c r="E27" s="188"/>
+      <c r="F27" s="189"/>
     </row>
     <row r="28" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="31"/>
       <c r="B28" s="25">
         <v>4</v>
       </c>
-      <c r="C28" s="171" t="s">
-        <v>103</v>
-      </c>
-      <c r="D28" s="172"/>
-      <c r="E28" s="172"/>
-      <c r="F28" s="173"/>
+      <c r="C28" s="190" t="s">
+        <v>102</v>
+      </c>
+      <c r="D28" s="191"/>
+      <c r="E28" s="191"/>
+      <c r="F28" s="192"/>
     </row>
     <row r="29" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="31"/>
       <c r="B29" s="25">
         <v>5</v>
       </c>
-      <c r="C29" s="180" t="s">
-        <v>87</v>
-      </c>
-      <c r="D29" s="181"/>
-      <c r="E29" s="181"/>
-      <c r="F29" s="182"/>
+      <c r="C29" s="171" t="s">
+        <v>86</v>
+      </c>
+      <c r="D29" s="172"/>
+      <c r="E29" s="172"/>
+      <c r="F29" s="173"/>
     </row>
     <row r="30" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="32"/>
       <c r="B30" s="27">
         <v>6</v>
       </c>
-      <c r="C30" s="199"/>
-      <c r="D30" s="200"/>
-      <c r="E30" s="200"/>
-      <c r="F30" s="201"/>
+      <c r="C30" s="193"/>
+      <c r="D30" s="194"/>
+      <c r="E30" s="194"/>
+      <c r="F30" s="195"/>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="33" t="s">
@@ -3485,56 +3485,56 @@
       <c r="B31" s="23">
         <v>2</v>
       </c>
-      <c r="C31" s="186"/>
-      <c r="D31" s="187"/>
-      <c r="E31" s="187"/>
-      <c r="F31" s="188"/>
+      <c r="C31" s="177"/>
+      <c r="D31" s="178"/>
+      <c r="E31" s="178"/>
+      <c r="F31" s="179"/>
     </row>
     <row r="32" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A32" s="34"/>
       <c r="B32" s="25">
         <v>3</v>
       </c>
-      <c r="C32" s="132" t="s">
-        <v>89</v>
-      </c>
-      <c r="D32" s="133"/>
-      <c r="E32" s="133"/>
-      <c r="F32" s="195"/>
+      <c r="C32" s="111" t="s">
+        <v>88</v>
+      </c>
+      <c r="D32" s="112"/>
+      <c r="E32" s="112"/>
+      <c r="F32" s="186"/>
     </row>
     <row r="33" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="35"/>
       <c r="B33" s="36">
         <v>4</v>
       </c>
-      <c r="C33" s="202"/>
-      <c r="D33" s="203"/>
-      <c r="E33" s="203"/>
-      <c r="F33" s="204"/>
+      <c r="C33" s="196"/>
+      <c r="D33" s="197"/>
+      <c r="E33" s="197"/>
+      <c r="F33" s="198"/>
     </row>
     <row r="34" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="65"/>
       <c r="B34" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="192" t="s">
-        <v>101</v>
-      </c>
-      <c r="D34" s="193"/>
-      <c r="E34" s="193"/>
-      <c r="F34" s="194"/>
+      <c r="C34" s="183" t="s">
+        <v>100</v>
+      </c>
+      <c r="D34" s="184"/>
+      <c r="E34" s="184"/>
+      <c r="F34" s="185"/>
     </row>
     <row r="35" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="57" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B35" s="58"/>
-      <c r="C35" s="152" t="s">
-        <v>63</v>
-      </c>
-      <c r="D35" s="152"/>
-      <c r="E35" s="152"/>
-      <c r="F35" s="152"/>
+      <c r="C35" s="142" t="s">
+        <v>62</v>
+      </c>
+      <c r="D35" s="142"/>
+      <c r="E35" s="142"/>
+      <c r="F35" s="142"/>
     </row>
     <row r="36" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A36" s="2" t="s">
@@ -3543,7 +3543,7 @@
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
@@ -3562,6 +3562,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C8:F8"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="C35:F35"/>
     <mergeCell ref="C22:F22"/>
@@ -3578,18 +3590,6 @@
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C8:F8"/>
   </mergeCells>
   <conditionalFormatting sqref="C8">
     <cfRule type="expression" priority="1">
@@ -3637,7 +3637,7 @@
     </row>
     <row r="2" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3661,14 +3661,14 @@
     </row>
     <row r="4" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
@@ -3708,10 +3708,10 @@
         <v>16</v>
       </c>
       <c r="B7" s="2"/>
-      <c r="C7" s="90" t="s">
+      <c r="C7" s="113" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="90"/>
+      <c r="D7" s="113"/>
       <c r="E7" s="40" t="s">
         <v>29</v>
       </c>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D9" s="55"/>
       <c r="E9" s="55"/>
@@ -3764,58 +3764,58 @@
       <c r="B11" s="23">
         <v>4</v>
       </c>
-      <c r="C11" s="101"/>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="71"/>
+      <c r="C11" s="118"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="119"/>
+      <c r="F11" s="124"/>
     </row>
     <row r="12" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="24"/>
       <c r="B12" s="25">
         <v>5</v>
       </c>
-      <c r="C12" s="74" t="s">
-        <v>90</v>
-      </c>
-      <c r="D12" s="72"/>
-      <c r="E12" s="211"/>
-      <c r="F12" s="212"/>
+      <c r="C12" s="79" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" s="80"/>
+      <c r="E12" s="226"/>
+      <c r="F12" s="227"/>
     </row>
     <row r="13" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="24"/>
       <c r="B13" s="25">
         <v>6</v>
       </c>
-      <c r="C13" s="74" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13" s="72"/>
-      <c r="E13" s="213"/>
-      <c r="F13" s="214"/>
+      <c r="C13" s="79" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" s="80"/>
+      <c r="E13" s="228"/>
+      <c r="F13" s="229"/>
     </row>
     <row r="14" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A14" s="24"/>
       <c r="B14" s="25">
         <v>7</v>
       </c>
-      <c r="C14" s="97" t="s">
+      <c r="C14" s="103" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="98"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="99"/>
+      <c r="D14" s="104"/>
+      <c r="E14" s="104"/>
+      <c r="F14" s="105"/>
     </row>
     <row r="15" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="26"/>
       <c r="B15" s="27">
         <v>8</v>
       </c>
-      <c r="C15" s="120" t="s">
-        <v>92</v>
-      </c>
-      <c r="D15" s="121"/>
-      <c r="E15" s="121"/>
-      <c r="F15" s="122"/>
+      <c r="C15" s="91" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="92"/>
+      <c r="E15" s="92"/>
+      <c r="F15" s="93"/>
     </row>
     <row r="16" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="28" t="s">
@@ -3824,58 +3824,58 @@
       <c r="B16" s="29">
         <v>2</v>
       </c>
-      <c r="C16" s="215"/>
-      <c r="D16" s="216"/>
-      <c r="E16" s="219" t="s">
-        <v>91</v>
-      </c>
-      <c r="F16" s="220"/>
+      <c r="C16" s="230"/>
+      <c r="D16" s="231"/>
+      <c r="E16" s="234" t="s">
+        <v>90</v>
+      </c>
+      <c r="F16" s="235"/>
     </row>
     <row r="17" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="24"/>
       <c r="B17" s="25">
         <v>3</v>
       </c>
-      <c r="C17" s="217"/>
-      <c r="D17" s="218"/>
-      <c r="E17" s="76" t="s">
-        <v>91</v>
-      </c>
-      <c r="F17" s="77"/>
+      <c r="C17" s="232"/>
+      <c r="D17" s="233"/>
+      <c r="E17" s="126" t="s">
+        <v>90</v>
+      </c>
+      <c r="F17" s="127"/>
     </row>
     <row r="18" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A18" s="24"/>
       <c r="B18" s="25">
         <v>4</v>
       </c>
-      <c r="C18" s="132" t="s">
-        <v>111</v>
-      </c>
-      <c r="D18" s="133"/>
-      <c r="E18" s="133"/>
-      <c r="F18" s="195"/>
+      <c r="C18" s="111" t="s">
+        <v>119</v>
+      </c>
+      <c r="D18" s="112"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="186"/>
     </row>
     <row r="19" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A19" s="24"/>
       <c r="B19" s="25">
         <v>5</v>
       </c>
-      <c r="C19" s="132" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" s="133"/>
-      <c r="E19" s="133"/>
-      <c r="F19" s="195"/>
+      <c r="C19" s="111" t="s">
+        <v>120</v>
+      </c>
+      <c r="D19" s="112"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="186"/>
     </row>
     <row r="20" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="30"/>
       <c r="B20" s="27">
         <v>6</v>
       </c>
-      <c r="C20" s="208"/>
-      <c r="D20" s="209"/>
-      <c r="E20" s="209"/>
-      <c r="F20" s="210"/>
+      <c r="C20" s="223"/>
+      <c r="D20" s="224"/>
+      <c r="E20" s="224"/>
+      <c r="F20" s="225"/>
     </row>
     <row r="21" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A21" s="28" t="s">
@@ -3884,44 +3884,44 @@
       <c r="B21" s="29">
         <v>2</v>
       </c>
-      <c r="C21" s="205"/>
-      <c r="D21" s="206"/>
-      <c r="E21" s="206"/>
-      <c r="F21" s="207"/>
+      <c r="C21" s="220"/>
+      <c r="D21" s="221"/>
+      <c r="E21" s="221"/>
+      <c r="F21" s="222"/>
     </row>
     <row r="22" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A22" s="24"/>
       <c r="B22" s="25">
         <v>3</v>
       </c>
-      <c r="C22" s="227"/>
-      <c r="D22" s="228"/>
-      <c r="E22" s="228"/>
-      <c r="F22" s="229"/>
+      <c r="C22" s="208"/>
+      <c r="D22" s="209"/>
+      <c r="E22" s="209"/>
+      <c r="F22" s="210"/>
     </row>
     <row r="23" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A23" s="24"/>
       <c r="B23" s="25">
         <v>4</v>
       </c>
-      <c r="C23" s="67" t="s">
-        <v>117</v>
-      </c>
-      <c r="D23" s="68"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="69"/>
+      <c r="C23" s="121" t="s">
+        <v>115</v>
+      </c>
+      <c r="D23" s="122"/>
+      <c r="E23" s="122"/>
+      <c r="F23" s="123"/>
     </row>
     <row r="24" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="30"/>
       <c r="B24" s="27">
         <v>5</v>
       </c>
-      <c r="C24" s="108" t="s">
+      <c r="C24" s="73" t="s">
         <v>40</v>
       </c>
-      <c r="D24" s="109"/>
-      <c r="E24" s="109"/>
-      <c r="F24" s="110"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="74"/>
+      <c r="F24" s="75"/>
     </row>
     <row r="25" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A25" s="28" t="s">
@@ -3930,48 +3930,48 @@
       <c r="B25" s="29">
         <v>1</v>
       </c>
-      <c r="C25" s="230" t="s">
-        <v>112</v>
-      </c>
-      <c r="D25" s="231"/>
-      <c r="E25" s="231"/>
-      <c r="F25" s="232"/>
+      <c r="C25" s="211" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" s="212"/>
+      <c r="E25" s="212"/>
+      <c r="F25" s="213"/>
     </row>
     <row r="26" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A26" s="24"/>
       <c r="B26" s="25">
         <v>2</v>
       </c>
-      <c r="C26" s="230" t="s">
-        <v>112</v>
-      </c>
-      <c r="D26" s="231"/>
-      <c r="E26" s="231"/>
-      <c r="F26" s="232"/>
+      <c r="C26" s="211" t="s">
+        <v>110</v>
+      </c>
+      <c r="D26" s="212"/>
+      <c r="E26" s="212"/>
+      <c r="F26" s="213"/>
     </row>
     <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="24"/>
       <c r="B27" s="25">
         <v>3</v>
       </c>
-      <c r="C27" s="105" t="s">
+      <c r="C27" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="D27" s="106"/>
-      <c r="E27" s="106"/>
-      <c r="F27" s="107"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="72"/>
     </row>
     <row r="28" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A28" s="30"/>
       <c r="B28" s="27">
         <v>4</v>
       </c>
-      <c r="C28" s="233" t="s">
+      <c r="C28" s="205" t="s">
         <v>41</v>
       </c>
-      <c r="D28" s="234"/>
-      <c r="E28" s="234"/>
-      <c r="F28" s="235"/>
+      <c r="D28" s="206"/>
+      <c r="E28" s="206"/>
+      <c r="F28" s="207"/>
     </row>
     <row r="29" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="28" t="s">
@@ -3980,52 +3980,52 @@
       <c r="B29" s="29">
         <v>1</v>
       </c>
-      <c r="C29" s="146" t="s">
-        <v>108</v>
-      </c>
-      <c r="D29" s="147"/>
-      <c r="E29" s="147"/>
-      <c r="F29" s="148"/>
+      <c r="C29" s="165" t="s">
+        <v>107</v>
+      </c>
+      <c r="D29" s="166"/>
+      <c r="E29" s="166"/>
+      <c r="F29" s="167"/>
     </row>
     <row r="30" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="31"/>
       <c r="B30" s="25">
         <v>2</v>
       </c>
-      <c r="C30" s="75" t="s">
-        <v>108</v>
-      </c>
-      <c r="D30" s="76"/>
-      <c r="E30" s="76"/>
-      <c r="F30" s="77"/>
+      <c r="C30" s="125" t="s">
+        <v>107</v>
+      </c>
+      <c r="D30" s="126"/>
+      <c r="E30" s="126"/>
+      <c r="F30" s="127"/>
     </row>
     <row r="31" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="31"/>
       <c r="B31" s="25">
         <v>3</v>
       </c>
-      <c r="C31" s="74" t="s">
+      <c r="C31" s="79" t="s">
+        <v>108</v>
+      </c>
+      <c r="D31" s="80"/>
+      <c r="E31" s="80" t="s">
         <v>109</v>
       </c>
-      <c r="D31" s="72"/>
-      <c r="E31" s="72" t="s">
-        <v>110</v>
-      </c>
-      <c r="F31" s="73"/>
+      <c r="F31" s="81"/>
     </row>
     <row r="32" spans="1:6" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A32" s="32"/>
       <c r="B32" s="27">
         <v>4</v>
       </c>
-      <c r="C32" s="224" t="s">
+      <c r="C32" s="217" t="s">
+        <v>108</v>
+      </c>
+      <c r="D32" s="218"/>
+      <c r="E32" s="218" t="s">
         <v>109</v>
       </c>
-      <c r="D32" s="225"/>
-      <c r="E32" s="225" t="s">
-        <v>110</v>
-      </c>
-      <c r="F32" s="226"/>
+      <c r="F32" s="219"/>
     </row>
     <row r="33" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A33" s="33" t="s">
@@ -4034,40 +4034,40 @@
       <c r="B33" s="23">
         <v>1</v>
       </c>
-      <c r="C33" s="117" t="s">
+      <c r="C33" s="88" t="s">
         <v>31</v>
       </c>
-      <c r="D33" s="118"/>
-      <c r="E33" s="118"/>
-      <c r="F33" s="119"/>
+      <c r="D33" s="89"/>
+      <c r="E33" s="89"/>
+      <c r="F33" s="90"/>
     </row>
     <row r="34" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A34" s="34"/>
       <c r="B34" s="25">
         <v>2</v>
       </c>
-      <c r="C34" s="126"/>
-      <c r="D34" s="127"/>
-      <c r="E34" s="127"/>
-      <c r="F34" s="128"/>
+      <c r="C34" s="100"/>
+      <c r="D34" s="101"/>
+      <c r="E34" s="101"/>
+      <c r="F34" s="102"/>
     </row>
     <row r="35" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A35" s="34"/>
       <c r="B35" s="25">
         <v>3</v>
       </c>
-      <c r="C35" s="126"/>
-      <c r="D35" s="127"/>
-      <c r="E35" s="127"/>
-      <c r="F35" s="128"/>
+      <c r="C35" s="100"/>
+      <c r="D35" s="101"/>
+      <c r="E35" s="101"/>
+      <c r="F35" s="102"/>
     </row>
     <row r="36" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A36" s="38"/>
       <c r="B36" s="54"/>
-      <c r="C36" s="221"/>
-      <c r="D36" s="222"/>
-      <c r="E36" s="222"/>
-      <c r="F36" s="223"/>
+      <c r="C36" s="214"/>
+      <c r="D36" s="215"/>
+      <c r="E36" s="215"/>
+      <c r="F36" s="216"/>
     </row>
     <row r="37" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A37" s="2" t="s">
@@ -4076,7 +4076,7 @@
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
@@ -4111,23 +4111,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="C33:F33"/>
     <mergeCell ref="C21:F21"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C11:F11"/>
@@ -4144,6 +4127,23 @@
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="E17:F17"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:E9">
     <cfRule type="expression" priority="2">

--- a/input/timetable/Прикладная математика и информатика.xlsx
+++ b/input/timetable/Прикладная математика и информатика.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="151">
   <si>
     <t>пара</t>
   </si>
@@ -71,6 +71,9 @@
     <t>Зав. кафедрой</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>Направление</t>
   </si>
   <si>
@@ -125,15 +128,36 @@
     <t>ТО</t>
   </si>
   <si>
+    <t>Веселов С.И.</t>
+  </si>
+  <si>
     <t>Физическая культура и спорт (лек 8 ч)</t>
   </si>
   <si>
+    <t>Ряховский А.В.</t>
+  </si>
+  <si>
+    <t>Шапошникова И.В.</t>
+  </si>
+  <si>
+    <t>Девицын И.Н.</t>
+  </si>
+  <si>
     <t>Математический анализ (лек), У704</t>
   </si>
   <si>
     <t>Математический анализ (пр), У704</t>
   </si>
   <si>
+    <t>Дубовик А.О.</t>
+  </si>
+  <si>
+    <t>Бычин И.В.</t>
+  </si>
+  <si>
+    <t>Назин А.Г.</t>
+  </si>
+  <si>
     <t>Иностранный язык, п/г 1, У508</t>
   </si>
   <si>
@@ -143,12 +167,27 @@
     <t>Дифференциальные уравнения (пр), У704</t>
   </si>
   <si>
+    <t>Галкин В.А.</t>
+  </si>
+  <si>
+    <t>Гореликов А.В.</t>
+  </si>
+  <si>
+    <t>Гавриленко Т.В.</t>
+  </si>
+  <si>
     <t>Основы математического моделирования (пр), У705</t>
   </si>
   <si>
     <t>Геоинформационные технологии (лаб), У705</t>
   </si>
   <si>
+    <t>Гимранов Р.Д.</t>
+  </si>
+  <si>
+    <t>Жебель В.А.</t>
+  </si>
+  <si>
     <t>Учебная практика, научно-исследовательская работа (получение первичных навыков научно-исследовательской работы), У705</t>
   </si>
   <si>
@@ -191,6 +230,9 @@
     <t>Алгоритмы и структуры данных, п/г2, У705</t>
   </si>
   <si>
+    <t>Семенов О.Ю.</t>
+  </si>
+  <si>
     <t>Математическая логика и теория алгоритмов (лек), У704</t>
   </si>
   <si>
@@ -212,6 +254,12 @@
     <t>Элект. дисциплины по физич. культуре и спорту проводятся  1 парой или  2 парой в зависимости от выбранной элективной дисциплины., занятия в объеме 16 часов провдятся по отдельному расписанию.</t>
   </si>
   <si>
+    <t>Бычин И.В.; Пичуева А.В.</t>
+  </si>
+  <si>
+    <t>Пешков А.А.</t>
+  </si>
+  <si>
     <t>Математический анализ (лек).У704// Информационные технологии (лек), У704</t>
   </si>
   <si>
@@ -239,12 +287,18 @@
     <t>История России (лек 32 ч)</t>
   </si>
   <si>
+    <t>Мягких К.П.</t>
+  </si>
+  <si>
     <t>Безопасность жизнедеятельности (лек 32 ч)</t>
   </si>
   <si>
     <t>Основы предпринимательской деятельности (лек 16 ч)</t>
   </si>
   <si>
+    <t>Смирнова И.В.</t>
+  </si>
+  <si>
     <t>Начальник УОпоОФО</t>
   </si>
   <si>
@@ -269,9 +323,21 @@
     <t>02.02.2026-08..04.2026</t>
   </si>
   <si>
+    <t>Ряховский А.В./Еловой С.Г.</t>
+  </si>
+  <si>
+    <t>Кучин И.А.</t>
+  </si>
+  <si>
+    <t>Чеснокова Н.Е.; Кучин И.А.</t>
+  </si>
+  <si>
     <t>Философия (лек 32 ч)</t>
   </si>
   <si>
+    <t>Никулина О.В.</t>
+  </si>
+  <si>
     <t>Методы оптимизации (лек), У704</t>
   </si>
   <si>
@@ -299,6 +365,9 @@
     <t>ФТД: Сети ЭВМ (пр), У705</t>
   </si>
   <si>
+    <t>Курц М.А.</t>
+  </si>
+  <si>
     <t>Иностранный язык в профессиональной сфере (пр 24ч), У507</t>
   </si>
   <si>
@@ -314,6 +383,15 @@
     <t>Физика (лек), А314</t>
   </si>
   <si>
+    <t>Никулина О.В./Семенов О.Ю.</t>
+  </si>
+  <si>
+    <t>Пичуева А.В.</t>
+  </si>
+  <si>
+    <t>Кузнецова С.В.; Бычин И.В.</t>
+  </si>
+  <si>
     <t>Философия (пр), А320// Физика (пр), А320</t>
   </si>
   <si>
@@ -326,9 +404,18 @@
     <t>Правоведение (лек 32 ч)</t>
   </si>
   <si>
+    <t>Ашарин А.А.</t>
+  </si>
+  <si>
     <t>Правоведение (пр), У704</t>
   </si>
   <si>
+    <t>Бурдыко Т.Г</t>
+  </si>
+  <si>
+    <t>.Бычин И.В.</t>
+  </si>
+  <si>
     <t>Разработка программного обеспечения в ОС Linux (лек), У705</t>
   </si>
   <si>
@@ -345,6 +432,9 @@
   </si>
   <si>
     <t>Технологии параллельного программирования (лек), У704</t>
+  </si>
+  <si>
+    <t>Сало В.Э.</t>
   </si>
   <si>
     <t>Иностранный язык в проф. сфере, п/г 1, У507//</t>
@@ -501,7 +591,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -520,12 +610,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="54">
+  <borders count="60">
     <border>
       <left/>
       <right/>
@@ -648,6 +744,64 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -784,6 +938,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -1144,6 +1311,15 @@
         <color indexed="64"/>
       </left>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -1206,7 +1382,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="236">
+  <cellXfs count="265">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1243,28 +1419,31 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1294,10 +1473,10 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1308,10 +1487,15 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1323,20 +1507,20 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1345,9 +1529,11 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1358,383 +1544,404 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2045,7 +2252,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2054,10 +2261,11 @@
     <col min="4" max="4" width="20.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="20.42578125" style="2" customWidth="1"/>
     <col min="6" max="6" width="19.7109375" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -2065,15 +2273,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -2081,39 +2289,39 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="63" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F4" s="74" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -2123,35 +2331,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="113" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="119" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="113"/>
-      <c r="E7" s="40" t="s">
-        <v>78</v>
+      <c r="D7" s="119"/>
+      <c r="E7" s="41" t="s">
+        <v>96</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="56" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="117" t="s">
-        <v>79</v>
-      </c>
-      <c r="D8" s="117"/>
-      <c r="E8" s="117"/>
-      <c r="F8" s="117"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="129" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8" s="129"/>
+      <c r="E8" s="129"/>
+      <c r="F8" s="129"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>0</v>
@@ -2162,358 +2370,433 @@
       <c r="D9" s="19"/>
       <c r="E9" s="20"/>
       <c r="F9" s="21"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="23">
+      <c r="G9" s="22" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="24">
         <v>1</v>
       </c>
-      <c r="C10" s="118"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="110" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="120"/>
-    </row>
-    <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="24"/>
-      <c r="B11" s="25">
+      <c r="C10" s="130"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="108" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" s="109"/>
+      <c r="G10" s="76" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="25"/>
+      <c r="B11" s="26">
         <v>2</v>
       </c>
-      <c r="C11" s="82" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" s="83"/>
-      <c r="E11" s="83" t="s">
-        <v>65</v>
-      </c>
-      <c r="F11" s="84"/>
-    </row>
-    <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="24"/>
-      <c r="B12" s="25">
+      <c r="C11" s="118" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" s="116"/>
+      <c r="E11" s="116" t="s">
+        <v>81</v>
+      </c>
+      <c r="F11" s="117"/>
+      <c r="G11" s="75" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="25"/>
+      <c r="B12" s="26">
         <v>3</v>
       </c>
-      <c r="C12" s="103" t="s">
+      <c r="C12" s="126" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="127"/>
+      <c r="E12" s="127"/>
+      <c r="F12" s="128"/>
+      <c r="G12" s="75" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" s="25"/>
+      <c r="B13" s="26">
+        <v>4</v>
+      </c>
+      <c r="C13" s="120" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="121"/>
+      <c r="E13" s="121"/>
+      <c r="F13" s="122"/>
+      <c r="G13" s="75" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="27"/>
+      <c r="B14" s="28">
+        <v>5</v>
+      </c>
+      <c r="C14" s="123"/>
+      <c r="D14" s="124"/>
+      <c r="E14" s="124"/>
+      <c r="F14" s="125"/>
+      <c r="G14" s="71"/>
+    </row>
+    <row r="15" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="30">
+        <v>1</v>
+      </c>
+      <c r="C15" s="131" t="s">
+        <v>117</v>
+      </c>
+      <c r="D15" s="132"/>
+      <c r="E15" s="132"/>
+      <c r="F15" s="133"/>
+      <c r="G15" s="76" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="25"/>
+      <c r="B16" s="26">
+        <v>2</v>
+      </c>
+      <c r="C16" s="134" t="s">
+        <v>118</v>
+      </c>
+      <c r="D16" s="135"/>
+      <c r="E16" s="135"/>
+      <c r="F16" s="136"/>
+      <c r="G16" s="75" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="25"/>
+      <c r="B17" s="26">
+        <v>3</v>
+      </c>
+      <c r="C17" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="105"/>
+      <c r="E17" s="105"/>
+      <c r="F17" s="106"/>
+      <c r="G17" s="75" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="31"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="110"/>
+      <c r="D18" s="111"/>
+      <c r="E18" s="111"/>
+      <c r="F18" s="112"/>
+      <c r="G18" s="71"/>
+    </row>
+    <row r="19" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="30">
+        <v>2</v>
+      </c>
+      <c r="C19" s="107" t="s">
+        <v>147</v>
+      </c>
+      <c r="D19" s="108"/>
+      <c r="E19" s="108"/>
+      <c r="F19" s="109"/>
+      <c r="G19" s="95" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="25"/>
+      <c r="B20" s="26">
+        <v>3</v>
+      </c>
+      <c r="C20" s="103" t="s">
+        <v>146</v>
+      </c>
+      <c r="D20" s="101"/>
+      <c r="E20" s="101"/>
+      <c r="F20" s="102"/>
+      <c r="G20" s="82" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="25"/>
+      <c r="B21" s="26">
+        <v>4</v>
+      </c>
+      <c r="C21" s="103" t="s">
+        <v>119</v>
+      </c>
+      <c r="D21" s="101"/>
+      <c r="E21" s="101"/>
+      <c r="F21" s="102"/>
+      <c r="G21" s="82" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="31"/>
+      <c r="B22" s="28">
+        <v>5</v>
+      </c>
+      <c r="C22" s="113" t="s">
+        <v>132</v>
+      </c>
+      <c r="D22" s="114"/>
+      <c r="E22" s="114" t="s">
+        <v>133</v>
+      </c>
+      <c r="F22" s="115"/>
+      <c r="G22" s="81" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="30">
+        <v>1</v>
+      </c>
+      <c r="C23" s="143" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" s="144"/>
+      <c r="E23" s="144"/>
+      <c r="F23" s="145"/>
+      <c r="G23" s="76" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="25"/>
+      <c r="B24" s="26">
+        <v>2</v>
+      </c>
+      <c r="C24" s="118" t="s">
+        <v>80</v>
+      </c>
+      <c r="D24" s="116"/>
+      <c r="E24" s="116"/>
+      <c r="F24" s="117"/>
+      <c r="G24" s="75" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="25"/>
+      <c r="B25" s="26">
+        <v>3</v>
+      </c>
+      <c r="C25" s="120" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" s="121"/>
+      <c r="E25" s="121"/>
+      <c r="F25" s="122"/>
+      <c r="G25" s="85" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="104"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="105"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13" s="24"/>
-      <c r="B13" s="25">
+    </row>
+    <row r="26" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="31"/>
+      <c r="B26" s="28">
+        <v>6</v>
+      </c>
+      <c r="C26" s="149" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="150"/>
+      <c r="E26" s="150"/>
+      <c r="F26" s="151"/>
+      <c r="G26" s="75" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="30">
+        <v>1</v>
+      </c>
+      <c r="C27" s="107" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" s="108"/>
+      <c r="E27" s="99"/>
+      <c r="F27" s="100"/>
+      <c r="G27" s="76" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="32"/>
+      <c r="B28" s="26">
+        <v>2</v>
+      </c>
+      <c r="C28" s="161" t="s">
+        <v>45</v>
+      </c>
+      <c r="D28" s="162"/>
+      <c r="E28" s="101" t="s">
+        <v>60</v>
+      </c>
+      <c r="F28" s="102"/>
+      <c r="G28" s="75" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A29" s="32"/>
+      <c r="B29" s="26">
+        <v>3</v>
+      </c>
+      <c r="C29" s="118" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29" s="116"/>
+      <c r="E29" s="116" t="s">
+        <v>116</v>
+      </c>
+      <c r="F29" s="117"/>
+      <c r="G29" s="85" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="33"/>
+      <c r="B30" s="28">
         <v>4</v>
       </c>
-      <c r="C13" s="97" t="s">
+      <c r="C30" s="152" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="153"/>
+      <c r="E30" s="153"/>
+      <c r="F30" s="154"/>
+      <c r="G30" s="86" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" s="24">
+        <v>2</v>
+      </c>
+      <c r="C31" s="146" t="s">
+        <v>72</v>
+      </c>
+      <c r="D31" s="147"/>
+      <c r="E31" s="147"/>
+      <c r="F31" s="148"/>
+      <c r="G31" s="46"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="35"/>
+      <c r="B32" s="26">
+        <v>3</v>
+      </c>
+      <c r="C32" s="155"/>
+      <c r="D32" s="156"/>
+      <c r="E32" s="156"/>
+      <c r="F32" s="157"/>
+      <c r="G32" s="73"/>
+    </row>
+    <row r="33" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="36"/>
+      <c r="B33" s="37">
+        <v>4</v>
+      </c>
+      <c r="C33" s="126"/>
+      <c r="D33" s="127"/>
+      <c r="E33" s="127"/>
+      <c r="F33" s="128"/>
+      <c r="G33" s="75"/>
+    </row>
+    <row r="34" spans="1:7" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="42"/>
+      <c r="B34" s="43"/>
+      <c r="C34" s="140"/>
+      <c r="D34" s="141"/>
+      <c r="E34" s="141"/>
+      <c r="F34" s="142"/>
+      <c r="G34" s="44"/>
+    </row>
+    <row r="35" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="38"/>
+      <c r="B35" s="49" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="158" t="s">
+        <v>87</v>
+      </c>
+      <c r="D35" s="159"/>
+      <c r="E35" s="159"/>
+      <c r="F35" s="160"/>
+      <c r="G35" s="80" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="69"/>
+      <c r="B36" s="70" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" s="96" t="s">
+        <v>89</v>
+      </c>
+      <c r="D36" s="97"/>
+      <c r="E36" s="97"/>
+      <c r="F36" s="98"/>
+      <c r="G36" s="75" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="39"/>
+      <c r="B37" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37" s="137" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="98"/>
-      <c r="E13" s="98"/>
-      <c r="F13" s="99"/>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="26"/>
-      <c r="B14" s="27">
-        <v>5</v>
-      </c>
-      <c r="C14" s="114"/>
-      <c r="D14" s="115"/>
-      <c r="E14" s="115"/>
-      <c r="F14" s="116"/>
-    </row>
-    <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="29">
-        <v>1</v>
-      </c>
-      <c r="C15" s="67" t="s">
-        <v>94</v>
-      </c>
-      <c r="D15" s="68"/>
-      <c r="E15" s="68"/>
-      <c r="F15" s="69"/>
-    </row>
-    <row r="16" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="24"/>
-      <c r="B16" s="25">
-        <v>2</v>
-      </c>
-      <c r="C16" s="70" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16" s="71"/>
-      <c r="E16" s="71"/>
-      <c r="F16" s="72"/>
-    </row>
-    <row r="17" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="24"/>
-      <c r="B17" s="25">
-        <v>3</v>
-      </c>
-      <c r="C17" s="125" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" s="126"/>
-      <c r="E17" s="126"/>
-      <c r="F17" s="127"/>
-    </row>
-    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="30"/>
-      <c r="B18" s="27"/>
-      <c r="C18" s="128"/>
-      <c r="D18" s="129"/>
-      <c r="E18" s="129"/>
-      <c r="F18" s="130"/>
-    </row>
-    <row r="19" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="29">
-        <v>2</v>
-      </c>
-      <c r="C19" s="109" t="s">
-        <v>117</v>
-      </c>
-      <c r="D19" s="110"/>
-      <c r="E19" s="110"/>
-      <c r="F19" s="120"/>
-    </row>
-    <row r="20" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="24"/>
-      <c r="B20" s="25">
-        <v>3</v>
-      </c>
-      <c r="C20" s="79" t="s">
-        <v>116</v>
-      </c>
-      <c r="D20" s="80"/>
-      <c r="E20" s="80"/>
-      <c r="F20" s="81"/>
-    </row>
-    <row r="21" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="24"/>
-      <c r="B21" s="25">
-        <v>4</v>
-      </c>
-      <c r="C21" s="79" t="s">
-        <v>96</v>
-      </c>
-      <c r="D21" s="80"/>
-      <c r="E21" s="80"/>
-      <c r="F21" s="81"/>
-    </row>
-    <row r="22" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="30"/>
-      <c r="B22" s="27">
-        <v>5</v>
-      </c>
-      <c r="C22" s="131" t="s">
-        <v>103</v>
-      </c>
-      <c r="D22" s="132"/>
-      <c r="E22" s="132" t="s">
-        <v>104</v>
-      </c>
-      <c r="F22" s="133"/>
-    </row>
-    <row r="23" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="29">
-        <v>1</v>
-      </c>
-      <c r="C23" s="85" t="s">
-        <v>63</v>
-      </c>
-      <c r="D23" s="86"/>
-      <c r="E23" s="86"/>
-      <c r="F23" s="87"/>
-    </row>
-    <row r="24" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="24"/>
-      <c r="B24" s="25">
-        <v>2</v>
-      </c>
-      <c r="C24" s="82" t="s">
-        <v>64</v>
-      </c>
-      <c r="D24" s="83"/>
-      <c r="E24" s="83"/>
-      <c r="F24" s="84"/>
-    </row>
-    <row r="25" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="24"/>
-      <c r="B25" s="25">
-        <v>3</v>
-      </c>
-      <c r="C25" s="97" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25" s="98"/>
-      <c r="E25" s="98"/>
-      <c r="F25" s="99"/>
-    </row>
-    <row r="26" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="30"/>
-      <c r="B26" s="27">
-        <v>6</v>
-      </c>
-      <c r="C26" s="91" t="s">
-        <v>50</v>
-      </c>
-      <c r="D26" s="92"/>
-      <c r="E26" s="92"/>
-      <c r="F26" s="93"/>
-    </row>
-    <row r="27" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="29">
-        <v>1</v>
-      </c>
-      <c r="C27" s="109" t="s">
-        <v>46</v>
-      </c>
-      <c r="D27" s="110"/>
-      <c r="E27" s="119"/>
-      <c r="F27" s="124"/>
-    </row>
-    <row r="28" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="31"/>
-      <c r="B28" s="25">
-        <v>2</v>
-      </c>
-      <c r="C28" s="111" t="s">
-        <v>37</v>
-      </c>
-      <c r="D28" s="112"/>
-      <c r="E28" s="80" t="s">
-        <v>47</v>
-      </c>
-      <c r="F28" s="81"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A29" s="31"/>
-      <c r="B29" s="25">
-        <v>3</v>
-      </c>
-      <c r="C29" s="82" t="s">
-        <v>48</v>
-      </c>
-      <c r="D29" s="83"/>
-      <c r="E29" s="83" t="s">
-        <v>93</v>
-      </c>
-      <c r="F29" s="84"/>
-    </row>
-    <row r="30" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="32"/>
-      <c r="B30" s="27">
-        <v>4</v>
-      </c>
-      <c r="C30" s="94" t="s">
-        <v>28</v>
-      </c>
-      <c r="D30" s="95"/>
-      <c r="E30" s="95"/>
-      <c r="F30" s="96"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="23">
-        <v>2</v>
-      </c>
-      <c r="C31" s="88" t="s">
-        <v>58</v>
-      </c>
-      <c r="D31" s="89"/>
-      <c r="E31" s="89"/>
-      <c r="F31" s="90"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="34"/>
-      <c r="B32" s="25">
-        <v>3</v>
-      </c>
-      <c r="C32" s="100"/>
-      <c r="D32" s="101"/>
-      <c r="E32" s="101"/>
-      <c r="F32" s="102"/>
-    </row>
-    <row r="33" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="35"/>
-      <c r="B33" s="36">
-        <v>4</v>
-      </c>
-      <c r="C33" s="103"/>
-      <c r="D33" s="104"/>
-      <c r="E33" s="104"/>
-      <c r="F33" s="105"/>
-    </row>
-    <row r="34" spans="1:6" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="41"/>
-      <c r="B34" s="42"/>
-      <c r="C34" s="76"/>
-      <c r="D34" s="77"/>
-      <c r="E34" s="77"/>
-      <c r="F34" s="78"/>
-    </row>
-    <row r="35" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="37"/>
-      <c r="B35" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="C35" s="106" t="s">
-        <v>71</v>
-      </c>
-      <c r="D35" s="107"/>
-      <c r="E35" s="107"/>
-      <c r="F35" s="108"/>
-    </row>
-    <row r="36" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="61"/>
-      <c r="B36" s="62" t="s">
-        <v>30</v>
-      </c>
-      <c r="C36" s="121" t="s">
-        <v>72</v>
-      </c>
-      <c r="D36" s="122"/>
-      <c r="E36" s="122"/>
-      <c r="F36" s="123"/>
-    </row>
-    <row r="37" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="38"/>
-      <c r="B37" s="39" t="s">
-        <v>30</v>
-      </c>
-      <c r="C37" s="73" t="s">
-        <v>34</v>
-      </c>
-      <c r="D37" s="74"/>
-      <c r="E37" s="74"/>
-      <c r="F37" s="75"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="D37" s="138"/>
+      <c r="E37" s="138"/>
+      <c r="F37" s="139"/>
+      <c r="G37" s="77" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A39" s="2" t="s">
         <v>15</v>
       </c>
@@ -2523,26 +2806,6 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C37:F37"/>
@@ -2559,6 +2822,26 @@
     <mergeCell ref="C35:F35"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="C29:D29"/>
   </mergeCells>
   <conditionalFormatting sqref="C8">
     <cfRule type="expression" priority="1">
@@ -2581,7 +2864,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2590,10 +2873,11 @@
     <col min="4" max="4" width="18.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="19.5703125" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -2601,15 +2885,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -2617,39 +2901,39 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="63" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="F4" s="74" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -2659,35 +2943,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="113" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="119" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="113"/>
-      <c r="E7" s="44" t="s">
-        <v>52</v>
+      <c r="D7" s="119"/>
+      <c r="E7" s="50" t="s">
+        <v>65</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="56" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="117" t="s">
-        <v>79</v>
-      </c>
-      <c r="D8" s="117"/>
-      <c r="E8" s="117"/>
-      <c r="F8" s="117"/>
-    </row>
-    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="129" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8" s="129"/>
+      <c r="E8" s="129"/>
+      <c r="F8" s="129"/>
+    </row>
+    <row r="9" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>0</v>
@@ -2698,340 +2982,402 @@
       <c r="D9" s="19"/>
       <c r="E9" s="20"/>
       <c r="F9" s="21"/>
-    </row>
-    <row r="10" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="29">
+      <c r="G9" s="22" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="30">
         <v>1</v>
       </c>
-      <c r="C10" s="160"/>
-      <c r="D10" s="140"/>
-      <c r="E10" s="139" t="s">
-        <v>65</v>
-      </c>
-      <c r="F10" s="161"/>
-      <c r="G10" s="64"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A11" s="24"/>
-      <c r="B11" s="25">
+      <c r="C10" s="168"/>
+      <c r="D10" s="169"/>
+      <c r="E10" s="170" t="s">
+        <v>81</v>
+      </c>
+      <c r="F10" s="171"/>
+      <c r="G10" s="87" t="s">
+        <v>121</v>
+      </c>
+      <c r="H10" s="89"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A11" s="25"/>
+      <c r="B11" s="26">
         <v>2</v>
       </c>
-      <c r="C11" s="125" t="s">
-        <v>97</v>
-      </c>
-      <c r="D11" s="126"/>
-      <c r="E11" s="126"/>
-      <c r="F11" s="127"/>
-    </row>
-    <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="24"/>
-      <c r="B12" s="25">
+      <c r="C11" s="104" t="s">
+        <v>123</v>
+      </c>
+      <c r="D11" s="105"/>
+      <c r="E11" s="105"/>
+      <c r="F11" s="106"/>
+      <c r="G11" s="85" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="25"/>
+      <c r="B12" s="26">
         <v>3</v>
       </c>
-      <c r="C12" s="125" t="s">
-        <v>98</v>
-      </c>
-      <c r="D12" s="126"/>
-      <c r="E12" s="126"/>
-      <c r="F12" s="127"/>
-    </row>
-    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="26"/>
-      <c r="B13" s="59" t="s">
+      <c r="C12" s="104" t="s">
+        <v>124</v>
+      </c>
+      <c r="D12" s="105"/>
+      <c r="E12" s="105"/>
+      <c r="F12" s="106"/>
+      <c r="G12" s="85" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="27"/>
+      <c r="B13" s="67" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="166"/>
+      <c r="E13" s="166"/>
+      <c r="F13" s="167"/>
+      <c r="G13" s="71"/>
+    </row>
+    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="30">
+        <v>3</v>
+      </c>
+      <c r="C14" s="172" t="s">
+        <v>84</v>
+      </c>
+      <c r="D14" s="173"/>
+      <c r="E14" s="173"/>
+      <c r="F14" s="174"/>
+      <c r="G14" s="76" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="25"/>
+      <c r="B15" s="26">
+        <v>4</v>
+      </c>
+      <c r="C15" s="103" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" s="101"/>
+      <c r="E15" s="101"/>
+      <c r="F15" s="102"/>
+      <c r="G15" s="75" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A16" s="25"/>
+      <c r="B16" s="26">
+        <v>5</v>
+      </c>
+      <c r="C16" s="178"/>
+      <c r="D16" s="179"/>
+      <c r="E16" s="179"/>
+      <c r="F16" s="180"/>
+      <c r="G16" s="85"/>
+    </row>
+    <row r="17" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="31"/>
+      <c r="B17" s="28">
+        <v>6</v>
+      </c>
+      <c r="C17" s="110"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="111"/>
+      <c r="F17" s="112"/>
+      <c r="G17" s="71"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A18" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="30">
+        <v>1</v>
+      </c>
+      <c r="C18" s="175" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="176"/>
+      <c r="E18" s="176"/>
+      <c r="F18" s="177"/>
+      <c r="G18" s="76" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A19" s="25"/>
+      <c r="B19" s="26">
+        <v>2</v>
+      </c>
+      <c r="C19" s="103" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" s="101"/>
+      <c r="E19" s="101"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="75" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A20" s="25"/>
+      <c r="B20" s="26">
+        <v>3</v>
+      </c>
+      <c r="C20" s="120" t="s">
+        <v>125</v>
+      </c>
+      <c r="D20" s="121"/>
+      <c r="E20" s="121"/>
+      <c r="F20" s="122"/>
+      <c r="G20" s="85" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="31"/>
+      <c r="B21" s="28">
+        <v>4</v>
+      </c>
+      <c r="C21" s="110"/>
+      <c r="D21" s="111"/>
+      <c r="E21" s="111"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="71"/>
+    </row>
+    <row r="22" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="30">
+        <v>1</v>
+      </c>
+      <c r="C22" s="198" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="157" t="s">
-        <v>61</v>
-      </c>
-      <c r="D13" s="158"/>
-      <c r="E13" s="158"/>
-      <c r="F13" s="159"/>
-    </row>
-    <row r="14" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="29">
+      <c r="D22" s="170"/>
+      <c r="E22" s="169"/>
+      <c r="F22" s="199"/>
+      <c r="G22" s="76" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="25"/>
+      <c r="B23" s="26">
+        <v>2</v>
+      </c>
+      <c r="C23" s="194" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" s="195"/>
+      <c r="E23" s="196" t="s">
+        <v>68</v>
+      </c>
+      <c r="F23" s="197"/>
+      <c r="G23" s="75" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="25"/>
+      <c r="B24" s="26">
         <v>3</v>
       </c>
-      <c r="C14" s="162" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="163"/>
-      <c r="E14" s="163"/>
-      <c r="F14" s="164"/>
-    </row>
-    <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="24"/>
-      <c r="B15" s="25">
+      <c r="C24" s="103" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" s="101"/>
+      <c r="E24" s="101"/>
+      <c r="F24" s="102"/>
+      <c r="G24" s="75" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="31"/>
+      <c r="B25" s="67" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="165" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25" s="166"/>
+      <c r="E25" s="166"/>
+      <c r="F25" s="167"/>
+      <c r="G25" s="71"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A26" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="30">
+        <v>2</v>
+      </c>
+      <c r="C26" s="158" t="s">
+        <v>134</v>
+      </c>
+      <c r="D26" s="163"/>
+      <c r="E26" s="164" t="s">
+        <v>135</v>
+      </c>
+      <c r="F26" s="160"/>
+      <c r="G26" s="76" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A27" s="32"/>
+      <c r="B27" s="26">
+        <v>3</v>
+      </c>
+      <c r="C27" s="103" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="101"/>
+      <c r="E27" s="101"/>
+      <c r="F27" s="102"/>
+      <c r="G27" s="75" t="s">
+        <v>44</v>
+      </c>
+      <c r="L27" s="51"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A28" s="32"/>
+      <c r="B28" s="26">
         <v>4</v>
       </c>
-      <c r="C15" s="79" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" s="80"/>
-      <c r="E15" s="80"/>
-      <c r="F15" s="81"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A16" s="24"/>
-      <c r="B16" s="25">
-        <v>5</v>
-      </c>
-      <c r="C16" s="168"/>
-      <c r="D16" s="169"/>
-      <c r="E16" s="169"/>
-      <c r="F16" s="170"/>
-    </row>
-    <row r="17" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="30"/>
-      <c r="B17" s="27">
-        <v>6</v>
-      </c>
-      <c r="C17" s="128"/>
-      <c r="D17" s="129"/>
-      <c r="E17" s="129"/>
-      <c r="F17" s="130"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A18" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="29">
+      <c r="C28" s="103" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28" s="101"/>
+      <c r="E28" s="101"/>
+      <c r="F28" s="102"/>
+      <c r="G28" s="85" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="33"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="182"/>
+      <c r="D29" s="183"/>
+      <c r="E29" s="183"/>
+      <c r="F29" s="184"/>
+      <c r="G29" s="71"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A30" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="30">
         <v>1</v>
       </c>
-      <c r="C18" s="165" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" s="166"/>
-      <c r="E18" s="166"/>
-      <c r="F18" s="167"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A19" s="24"/>
-      <c r="B19" s="25">
+      <c r="C30" s="146" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" s="147"/>
+      <c r="E30" s="147"/>
+      <c r="F30" s="148"/>
+      <c r="G30" s="45"/>
+    </row>
+    <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="35"/>
+      <c r="B31" s="26">
         <v>2</v>
       </c>
-      <c r="C19" s="79" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" s="80"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="81"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A20" s="24"/>
-      <c r="B20" s="25">
+      <c r="C31" s="185"/>
+      <c r="D31" s="186"/>
+      <c r="E31" s="186"/>
+      <c r="F31" s="187"/>
+      <c r="G31" s="73"/>
+    </row>
+    <row r="32" spans="1:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="53"/>
+      <c r="B32" s="28">
         <v>3</v>
       </c>
-      <c r="C20" s="97" t="s">
-        <v>99</v>
-      </c>
-      <c r="D20" s="98"/>
-      <c r="E20" s="98"/>
-      <c r="F20" s="99"/>
-    </row>
-    <row r="21" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="30"/>
-      <c r="B21" s="27">
-        <v>4</v>
-      </c>
-      <c r="C21" s="128"/>
-      <c r="D21" s="129"/>
-      <c r="E21" s="129"/>
-      <c r="F21" s="130"/>
-    </row>
-    <row r="22" spans="1:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="29">
-        <v>1</v>
-      </c>
-      <c r="C22" s="138" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" s="139"/>
-      <c r="E22" s="140"/>
-      <c r="F22" s="141"/>
-    </row>
-    <row r="23" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="24"/>
-      <c r="B23" s="25">
-        <v>2</v>
-      </c>
-      <c r="C23" s="134" t="s">
-        <v>37</v>
-      </c>
-      <c r="D23" s="135"/>
-      <c r="E23" s="136" t="s">
-        <v>55</v>
-      </c>
-      <c r="F23" s="137"/>
-    </row>
-    <row r="24" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="24"/>
-      <c r="B24" s="25">
-        <v>3</v>
-      </c>
-      <c r="C24" s="79" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="80"/>
-      <c r="E24" s="80"/>
-      <c r="F24" s="81"/>
-    </row>
-    <row r="25" spans="1:11" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="30"/>
-      <c r="B25" s="59" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25" s="157" t="s">
-        <v>61</v>
-      </c>
-      <c r="D25" s="158"/>
-      <c r="E25" s="158"/>
-      <c r="F25" s="159"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A26" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="29">
-        <v>2</v>
-      </c>
-      <c r="C26" s="106" t="s">
-        <v>105</v>
-      </c>
-      <c r="D26" s="155"/>
-      <c r="E26" s="156" t="s">
-        <v>106</v>
-      </c>
-      <c r="F26" s="108"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A27" s="31"/>
-      <c r="B27" s="25">
-        <v>3</v>
-      </c>
-      <c r="C27" s="79" t="s">
-        <v>38</v>
-      </c>
-      <c r="D27" s="80"/>
-      <c r="E27" s="80"/>
-      <c r="F27" s="81"/>
-      <c r="K27" s="45"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A28" s="31"/>
-      <c r="B28" s="25">
-        <v>4</v>
-      </c>
-      <c r="C28" s="79" t="s">
-        <v>39</v>
-      </c>
-      <c r="D28" s="80"/>
-      <c r="E28" s="80"/>
-      <c r="F28" s="81"/>
-    </row>
-    <row r="29" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="32"/>
-      <c r="B29" s="27"/>
-      <c r="C29" s="143"/>
-      <c r="D29" s="144"/>
-      <c r="E29" s="144"/>
-      <c r="F29" s="145"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A30" s="46" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" s="29">
-        <v>1</v>
-      </c>
-      <c r="C30" s="88" t="s">
-        <v>58</v>
-      </c>
-      <c r="D30" s="89"/>
-      <c r="E30" s="89"/>
-      <c r="F30" s="90"/>
-    </row>
-    <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="34"/>
-      <c r="B31" s="25">
-        <v>2</v>
-      </c>
-      <c r="C31" s="146"/>
-      <c r="D31" s="147"/>
-      <c r="E31" s="147"/>
-      <c r="F31" s="148"/>
-    </row>
-    <row r="32" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="47"/>
-      <c r="B32" s="27">
-        <v>3</v>
-      </c>
-      <c r="C32" s="149"/>
-      <c r="D32" s="150"/>
-      <c r="E32" s="150"/>
-      <c r="F32" s="151"/>
-    </row>
-    <row r="33" spans="1:6" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="48"/>
-      <c r="B33" s="49"/>
-      <c r="C33" s="152"/>
-      <c r="D33" s="153"/>
-      <c r="E33" s="153"/>
-      <c r="F33" s="154"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A34" s="37"/>
-      <c r="B34" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="C34" s="106" t="s">
+      <c r="C32" s="188"/>
+      <c r="D32" s="189"/>
+      <c r="E32" s="189"/>
+      <c r="F32" s="190"/>
+      <c r="G32" s="71"/>
+    </row>
+    <row r="33" spans="1:7" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="54"/>
+      <c r="B33" s="55"/>
+      <c r="C33" s="191"/>
+      <c r="D33" s="192"/>
+      <c r="E33" s="192"/>
+      <c r="F33" s="193"/>
+      <c r="G33" s="88"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34" s="38"/>
+      <c r="B34" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34" s="158" t="s">
+        <v>90</v>
+      </c>
+      <c r="D34" s="159"/>
+      <c r="E34" s="159"/>
+      <c r="F34" s="160"/>
+      <c r="G34" s="80" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="39"/>
+      <c r="B35" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="137" t="s">
+        <v>103</v>
+      </c>
+      <c r="D35" s="138"/>
+      <c r="E35" s="138"/>
+      <c r="F35" s="139"/>
+      <c r="G35" s="77" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="65" t="s">
         <v>73</v>
       </c>
-      <c r="D34" s="107"/>
-      <c r="E34" s="107"/>
-      <c r="F34" s="108"/>
-    </row>
-    <row r="35" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="38"/>
-      <c r="B35" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="C35" s="73" t="s">
+      <c r="B36" s="66"/>
+      <c r="C36" s="181" t="s">
         <v>82</v>
       </c>
-      <c r="D35" s="74"/>
-      <c r="E35" s="74"/>
-      <c r="F35" s="75"/>
-    </row>
-    <row r="36" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="57" t="s">
-        <v>59</v>
-      </c>
-      <c r="B36" s="58"/>
-      <c r="C36" s="142" t="s">
-        <v>66</v>
-      </c>
-      <c r="D36" s="142"/>
-      <c r="E36" s="142"/>
-      <c r="F36" s="142"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="D36" s="181"/>
+      <c r="E36" s="181"/>
+      <c r="F36" s="181"/>
+      <c r="G36" s="64"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38" s="2" t="s">
         <v>15</v>
       </c>
@@ -3041,6 +3387,23 @@
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C28:F28"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="C7:D7"/>
@@ -3057,23 +3420,6 @@
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
   </mergeCells>
   <conditionalFormatting sqref="C8">
     <cfRule type="expression" priority="1">
@@ -3096,7 +3442,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.85546875" customWidth="1"/>
@@ -3105,9 +3451,10 @@
     <col min="4" max="4" width="18.28515625" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="19.42578125" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -3118,10 +3465,11 @@
       <c r="F1" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3130,8 +3478,9 @@
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -3142,42 +3491,45 @@
       <c r="F3" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+        <v>94</v>
+      </c>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="9" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -3186,369 +3538,434 @@
       <c r="F6" s="11" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="56" t="s">
-        <v>16</v>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="63" t="s">
+        <v>17</v>
       </c>
       <c r="B7" s="2"/>
-      <c r="C7" s="113" t="s">
+      <c r="C7" s="119" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="113"/>
-      <c r="E7" s="40" t="s">
-        <v>43</v>
+      <c r="D7" s="119"/>
+      <c r="E7" s="41" t="s">
+        <v>56</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="56" t="s">
-        <v>26</v>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="63" t="s">
+        <v>27</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="117" t="s">
-        <v>80</v>
-      </c>
-      <c r="D8" s="117"/>
-      <c r="E8" s="117"/>
-      <c r="F8" s="117"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C8" s="129" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" s="129"/>
+      <c r="E8" s="129"/>
+      <c r="F8" s="129"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="50" t="s">
+      <c r="C9" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="51"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="53"/>
-    </row>
-    <row r="10" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A10" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="23">
+      <c r="D9" s="57"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="22" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A10" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="24">
         <v>1</v>
       </c>
-      <c r="C10" s="85" t="s">
-        <v>111</v>
-      </c>
-      <c r="D10" s="86"/>
-      <c r="E10" s="86"/>
-      <c r="F10" s="87"/>
-    </row>
-    <row r="11" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A11" s="24"/>
-      <c r="B11" s="25">
+      <c r="C10" s="143" t="s">
+        <v>141</v>
+      </c>
+      <c r="D10" s="144"/>
+      <c r="E10" s="144"/>
+      <c r="F10" s="145"/>
+      <c r="G10" s="80" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A11" s="25"/>
+      <c r="B11" s="26">
         <v>2</v>
       </c>
-      <c r="C11" s="121" t="s">
-        <v>101</v>
-      </c>
-      <c r="D11" s="122"/>
-      <c r="E11" s="122"/>
-      <c r="F11" s="123"/>
-    </row>
-    <row r="12" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A12" s="24"/>
-      <c r="B12" s="25">
+      <c r="C11" s="96" t="s">
+        <v>128</v>
+      </c>
+      <c r="D11" s="97"/>
+      <c r="E11" s="97"/>
+      <c r="F11" s="98"/>
+      <c r="G11" s="79" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A12" s="25"/>
+      <c r="B12" s="26">
         <v>3</v>
       </c>
-      <c r="C12" s="97" t="s">
-        <v>87</v>
-      </c>
-      <c r="D12" s="98"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="99"/>
-    </row>
-    <row r="13" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="24"/>
-      <c r="B13" s="25">
+      <c r="C12" s="120" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" s="121"/>
+      <c r="E12" s="121"/>
+      <c r="F12" s="122"/>
+      <c r="G12" s="79" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="25"/>
+      <c r="B13" s="26">
         <v>4</v>
       </c>
-      <c r="C13" s="190" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="191"/>
-      <c r="E13" s="191"/>
-      <c r="F13" s="192"/>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="26"/>
-      <c r="B14" s="27">
+      <c r="C13" s="200" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="201"/>
+      <c r="E13" s="201"/>
+      <c r="F13" s="202"/>
+      <c r="G13" s="79" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="27"/>
+      <c r="B14" s="28">
         <v>5</v>
       </c>
-      <c r="C14" s="199"/>
-      <c r="D14" s="200"/>
-      <c r="E14" s="200"/>
-      <c r="F14" s="201"/>
-    </row>
-    <row r="15" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A15" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="29">
+      <c r="C14" s="203"/>
+      <c r="D14" s="204"/>
+      <c r="E14" s="204"/>
+      <c r="F14" s="205"/>
+      <c r="G14" s="48"/>
+    </row>
+    <row r="15" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A15" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="30">
         <v>4</v>
       </c>
-      <c r="C15" s="97" t="s">
-        <v>92</v>
-      </c>
-      <c r="D15" s="98"/>
-      <c r="E15" s="98"/>
-      <c r="F15" s="99"/>
-    </row>
-    <row r="16" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A16" s="24"/>
-      <c r="B16" s="25">
+      <c r="C15" s="120" t="s">
+        <v>115</v>
+      </c>
+      <c r="D15" s="121"/>
+      <c r="E15" s="121"/>
+      <c r="F15" s="122"/>
+      <c r="G15" s="79" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A16" s="25"/>
+      <c r="B16" s="26">
         <v>5</v>
       </c>
-      <c r="C16" s="190" t="s">
-        <v>83</v>
-      </c>
-      <c r="D16" s="191"/>
-      <c r="E16" s="191"/>
-      <c r="F16" s="192"/>
-    </row>
-    <row r="17" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="24"/>
-      <c r="B17" s="25">
+      <c r="C16" s="200" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" s="201"/>
+      <c r="E16" s="201"/>
+      <c r="F16" s="202"/>
+      <c r="G16" s="79" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="25"/>
+      <c r="B17" s="26">
         <v>6</v>
       </c>
-      <c r="C17" s="70" t="s">
-        <v>84</v>
-      </c>
-      <c r="D17" s="71"/>
-      <c r="E17" s="71"/>
-      <c r="F17" s="72"/>
-    </row>
-    <row r="18" spans="1:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="30"/>
-      <c r="B18" s="27"/>
-      <c r="C18" s="202"/>
-      <c r="D18" s="203"/>
-      <c r="E18" s="203"/>
-      <c r="F18" s="204"/>
-      <c r="L18" s="60"/>
-    </row>
-    <row r="19" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="29">
+      <c r="C17" s="134" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" s="135"/>
+      <c r="E17" s="135"/>
+      <c r="F17" s="136"/>
+      <c r="G17" s="79" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="31"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="206"/>
+      <c r="D18" s="207"/>
+      <c r="E18" s="207"/>
+      <c r="F18" s="208"/>
+      <c r="G18" s="48"/>
+      <c r="M18" s="68"/>
+    </row>
+    <row r="19" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="30">
         <v>1</v>
       </c>
-      <c r="C19" s="138" t="s">
-        <v>112</v>
-      </c>
-      <c r="D19" s="139"/>
-      <c r="E19" s="139"/>
-      <c r="F19" s="161"/>
-    </row>
-    <row r="20" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="24"/>
-      <c r="B20" s="25">
+      <c r="C19" s="198" t="s">
+        <v>142</v>
+      </c>
+      <c r="D19" s="170"/>
+      <c r="E19" s="170"/>
+      <c r="F19" s="171"/>
+      <c r="G19" s="76" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="25"/>
+      <c r="B20" s="26">
         <v>2</v>
       </c>
-      <c r="C20" s="171" t="s">
-        <v>113</v>
-      </c>
-      <c r="D20" s="172"/>
-      <c r="E20" s="172"/>
-      <c r="F20" s="173"/>
-    </row>
-    <row r="21" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="24"/>
-      <c r="B21" s="25">
+      <c r="C20" s="209" t="s">
+        <v>143</v>
+      </c>
+      <c r="D20" s="210"/>
+      <c r="E20" s="210"/>
+      <c r="F20" s="211"/>
+      <c r="G20" s="78" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="25"/>
+      <c r="B21" s="26">
         <v>3</v>
       </c>
-      <c r="C21" s="171" t="s">
-        <v>114</v>
-      </c>
-      <c r="D21" s="172"/>
-      <c r="E21" s="172"/>
-      <c r="F21" s="173"/>
-    </row>
-    <row r="22" spans="1:12" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="30"/>
-      <c r="B22" s="27">
+      <c r="C21" s="209" t="s">
+        <v>144</v>
+      </c>
+      <c r="D21" s="210"/>
+      <c r="E21" s="210"/>
+      <c r="F21" s="211"/>
+      <c r="G21" s="75" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="31"/>
+      <c r="B22" s="28">
         <v>4</v>
       </c>
-      <c r="C22" s="174"/>
-      <c r="D22" s="175"/>
-      <c r="E22" s="175"/>
-      <c r="F22" s="176"/>
-    </row>
-    <row r="23" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A23" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="29">
+      <c r="C22" s="212"/>
+      <c r="D22" s="213"/>
+      <c r="E22" s="213"/>
+      <c r="F22" s="214"/>
+      <c r="G22" s="71"/>
+    </row>
+    <row r="23" spans="1:13" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A23" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="30">
         <v>2</v>
       </c>
-      <c r="C23" s="85" t="s">
-        <v>118</v>
-      </c>
-      <c r="D23" s="86"/>
-      <c r="E23" s="86"/>
-      <c r="F23" s="87"/>
-    </row>
-    <row r="24" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A24" s="24"/>
-      <c r="B24" s="25">
+      <c r="C23" s="143" t="s">
+        <v>148</v>
+      </c>
+      <c r="D23" s="144"/>
+      <c r="E23" s="144"/>
+      <c r="F23" s="145"/>
+      <c r="G23" s="80" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A24" s="25"/>
+      <c r="B24" s="26">
         <v>3</v>
       </c>
-      <c r="C24" s="121" t="s">
-        <v>85</v>
-      </c>
-      <c r="D24" s="122"/>
-      <c r="E24" s="122"/>
-      <c r="F24" s="123"/>
-    </row>
-    <row r="25" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A25" s="24"/>
-      <c r="B25" s="25">
+      <c r="C24" s="96" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" s="97"/>
+      <c r="E24" s="97"/>
+      <c r="F24" s="98"/>
+      <c r="G24" s="79" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A25" s="25"/>
+      <c r="B25" s="26">
         <v>4</v>
       </c>
-      <c r="C25" s="171"/>
-      <c r="D25" s="172"/>
-      <c r="E25" s="172"/>
-      <c r="F25" s="173"/>
-    </row>
-    <row r="26" spans="1:12" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="30"/>
-      <c r="B26" s="27">
+      <c r="C25" s="209"/>
+      <c r="D25" s="210"/>
+      <c r="E25" s="210"/>
+      <c r="F25" s="211"/>
+      <c r="G25" s="79"/>
+    </row>
+    <row r="26" spans="1:13" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="31"/>
+      <c r="B26" s="28">
         <v>5</v>
       </c>
-      <c r="C26" s="180"/>
-      <c r="D26" s="181"/>
-      <c r="E26" s="181"/>
-      <c r="F26" s="182"/>
-    </row>
-    <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="C27" s="187" t="s">
-        <v>61</v>
-      </c>
-      <c r="D27" s="188"/>
-      <c r="E27" s="188"/>
-      <c r="F27" s="189"/>
-    </row>
-    <row r="28" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="31"/>
-      <c r="B28" s="25">
+      <c r="C26" s="218"/>
+      <c r="D26" s="219"/>
+      <c r="E26" s="219"/>
+      <c r="F26" s="220"/>
+      <c r="G26" s="77"/>
+    </row>
+    <row r="27" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" s="225" t="s">
+        <v>75</v>
+      </c>
+      <c r="D27" s="226"/>
+      <c r="E27" s="226"/>
+      <c r="F27" s="227"/>
+      <c r="G27" s="47"/>
+    </row>
+    <row r="28" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="32"/>
+      <c r="B28" s="26">
         <v>4</v>
       </c>
-      <c r="C28" s="190" t="s">
-        <v>102</v>
-      </c>
-      <c r="D28" s="191"/>
-      <c r="E28" s="191"/>
-      <c r="F28" s="192"/>
-    </row>
-    <row r="29" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="31"/>
-      <c r="B29" s="25">
+      <c r="C28" s="200" t="s">
+        <v>131</v>
+      </c>
+      <c r="D28" s="201"/>
+      <c r="E28" s="201"/>
+      <c r="F28" s="202"/>
+      <c r="G28" s="79" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="32"/>
+      <c r="B29" s="26">
         <v>5</v>
       </c>
-      <c r="C29" s="171" t="s">
-        <v>86</v>
-      </c>
-      <c r="D29" s="172"/>
-      <c r="E29" s="172"/>
-      <c r="F29" s="173"/>
-    </row>
-    <row r="30" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="32"/>
-      <c r="B30" s="27">
+      <c r="C29" s="209" t="s">
+        <v>108</v>
+      </c>
+      <c r="D29" s="210"/>
+      <c r="E29" s="210"/>
+      <c r="F29" s="211"/>
+      <c r="G29" s="79" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="33"/>
+      <c r="B30" s="28">
         <v>6</v>
       </c>
-      <c r="C30" s="193"/>
-      <c r="D30" s="194"/>
-      <c r="E30" s="194"/>
-      <c r="F30" s="195"/>
-    </row>
-    <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="23">
+      <c r="C30" s="228"/>
+      <c r="D30" s="229"/>
+      <c r="E30" s="229"/>
+      <c r="F30" s="230"/>
+      <c r="G30" s="48"/>
+    </row>
+    <row r="31" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" s="24">
         <v>2</v>
       </c>
-      <c r="C31" s="177"/>
-      <c r="D31" s="178"/>
-      <c r="E31" s="178"/>
-      <c r="F31" s="179"/>
-    </row>
-    <row r="32" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A32" s="34"/>
-      <c r="B32" s="25">
+      <c r="C31" s="215"/>
+      <c r="D31" s="216"/>
+      <c r="E31" s="216"/>
+      <c r="F31" s="217"/>
+      <c r="G31" s="72"/>
+    </row>
+    <row r="32" spans="1:13" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A32" s="35"/>
+      <c r="B32" s="26">
         <v>3</v>
       </c>
-      <c r="C32" s="111" t="s">
-        <v>88</v>
-      </c>
-      <c r="D32" s="112"/>
-      <c r="E32" s="112"/>
-      <c r="F32" s="186"/>
-    </row>
-    <row r="33" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="35"/>
-      <c r="B33" s="36">
+      <c r="C32" s="161" t="s">
+        <v>110</v>
+      </c>
+      <c r="D32" s="162"/>
+      <c r="E32" s="162"/>
+      <c r="F32" s="224"/>
+      <c r="G32" s="75" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="36"/>
+      <c r="B33" s="37">
         <v>4</v>
       </c>
-      <c r="C33" s="196"/>
-      <c r="D33" s="197"/>
-      <c r="E33" s="197"/>
-      <c r="F33" s="198"/>
-    </row>
-    <row r="34" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="65"/>
-      <c r="B34" s="66" t="s">
-        <v>30</v>
-      </c>
-      <c r="C34" s="183" t="s">
-        <v>100</v>
-      </c>
-      <c r="D34" s="184"/>
-      <c r="E34" s="184"/>
-      <c r="F34" s="185"/>
-    </row>
-    <row r="35" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="57" t="s">
-        <v>59</v>
-      </c>
-      <c r="B35" s="58"/>
-      <c r="C35" s="142" t="s">
-        <v>62</v>
-      </c>
-      <c r="D35" s="142"/>
-      <c r="E35" s="142"/>
-      <c r="F35" s="142"/>
-    </row>
-    <row r="36" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="C33" s="231"/>
+      <c r="D33" s="232"/>
+      <c r="E33" s="232"/>
+      <c r="F33" s="233"/>
+      <c r="G33" s="90"/>
+    </row>
+    <row r="34" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="91"/>
+      <c r="B34" s="92" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34" s="221" t="s">
+        <v>126</v>
+      </c>
+      <c r="D34" s="222"/>
+      <c r="E34" s="222"/>
+      <c r="F34" s="223"/>
+      <c r="G34" s="93" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="65" t="s">
+        <v>73</v>
+      </c>
+      <c r="B35" s="66"/>
+      <c r="C35" s="181" t="s">
+        <v>76</v>
+      </c>
+      <c r="D35" s="181"/>
+      <c r="E35" s="181"/>
+      <c r="F35" s="181"/>
+      <c r="G35" s="64"/>
+    </row>
+    <row r="36" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A36" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
-    </row>
-    <row r="37" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="G36" s="2"/>
+    </row>
+    <row r="37" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A37" s="2" t="s">
         <v>15</v>
       </c>
@@ -3559,21 +3976,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C8:F8"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="C35:F35"/>
     <mergeCell ref="C22:F22"/>
@@ -3590,6 +3996,18 @@
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C8:F8"/>
   </mergeCells>
   <conditionalFormatting sqref="C8">
     <cfRule type="expression" priority="1">
@@ -3612,7 +4030,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.85546875" customWidth="1"/>
@@ -3621,9 +4039,10 @@
     <col min="4" max="4" width="18.28515625" customWidth="1"/>
     <col min="5" max="5" width="19.28515625" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -3634,10 +4053,11 @@
       <c r="F1" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3646,8 +4066,9 @@
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -3658,42 +4079,45 @@
       <c r="F3" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+        <v>94</v>
+      </c>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="9" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -3702,50 +4126,54 @@
       <c r="F6" s="11" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="56" t="s">
-        <v>16</v>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="63" t="s">
+        <v>17</v>
       </c>
       <c r="B7" s="2"/>
-      <c r="C7" s="113" t="s">
+      <c r="C7" s="119" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="113"/>
-      <c r="E7" s="40" t="s">
-        <v>29</v>
+      <c r="D7" s="119"/>
+      <c r="E7" s="41" t="s">
+        <v>30</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="55"/>
-      <c r="E8" s="55"/>
+        <v>19</v>
+      </c>
+      <c r="D8" s="61"/>
+      <c r="E8" s="61"/>
       <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="D9" s="55"/>
-      <c r="E9" s="55"/>
+        <v>99</v>
+      </c>
+      <c r="D9" s="61"/>
+      <c r="E9" s="61"/>
       <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>0</v>
@@ -3756,332 +4184,398 @@
       <c r="D10" s="19"/>
       <c r="E10" s="20"/>
       <c r="F10" s="21"/>
-    </row>
-    <row r="11" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A11" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="23">
+      <c r="G10" s="22" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A11" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="24">
         <v>4</v>
       </c>
-      <c r="C11" s="118"/>
-      <c r="D11" s="119"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="124"/>
-    </row>
-    <row r="12" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="24"/>
-      <c r="B12" s="25">
+      <c r="C11" s="130"/>
+      <c r="D11" s="99"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="100"/>
+      <c r="G11" s="84"/>
+    </row>
+    <row r="12" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="25"/>
+      <c r="B12" s="26">
         <v>5</v>
       </c>
-      <c r="C12" s="79" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12" s="80"/>
-      <c r="E12" s="226"/>
-      <c r="F12" s="227"/>
-    </row>
-    <row r="13" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="24"/>
-      <c r="B13" s="25">
+      <c r="C12" s="103" t="s">
+        <v>111</v>
+      </c>
+      <c r="D12" s="101"/>
+      <c r="E12" s="240"/>
+      <c r="F12" s="241"/>
+      <c r="G12" s="85" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="25"/>
+      <c r="B13" s="26">
         <v>6</v>
       </c>
-      <c r="C13" s="79" t="s">
-        <v>89</v>
-      </c>
-      <c r="D13" s="80"/>
-      <c r="E13" s="228"/>
-      <c r="F13" s="229"/>
-    </row>
-    <row r="14" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A14" s="24"/>
-      <c r="B14" s="25">
+      <c r="C13" s="103" t="s">
+        <v>111</v>
+      </c>
+      <c r="D13" s="101"/>
+      <c r="E13" s="242"/>
+      <c r="F13" s="243"/>
+      <c r="G13" s="85" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A14" s="25"/>
+      <c r="B14" s="26">
         <v>7</v>
       </c>
-      <c r="C14" s="103" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="104"/>
-      <c r="E14" s="104"/>
-      <c r="F14" s="105"/>
-    </row>
-    <row r="15" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="26"/>
-      <c r="B15" s="27">
+      <c r="C14" s="126" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="127"/>
+      <c r="E14" s="127"/>
+      <c r="F14" s="128"/>
+      <c r="G14" s="85" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="27"/>
+      <c r="B15" s="28">
         <v>8</v>
       </c>
-      <c r="C15" s="91" t="s">
-        <v>91</v>
-      </c>
-      <c r="D15" s="92"/>
-      <c r="E15" s="92"/>
-      <c r="F15" s="93"/>
-    </row>
-    <row r="16" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="29">
+      <c r="C15" s="149" t="s">
+        <v>113</v>
+      </c>
+      <c r="D15" s="150"/>
+      <c r="E15" s="150"/>
+      <c r="F15" s="151"/>
+      <c r="G15" s="86" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="30">
         <v>2</v>
       </c>
-      <c r="C16" s="230"/>
-      <c r="D16" s="231"/>
-      <c r="E16" s="234" t="s">
-        <v>90</v>
-      </c>
-      <c r="F16" s="235"/>
-    </row>
-    <row r="17" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="24"/>
-      <c r="B17" s="25">
+      <c r="C16" s="244"/>
+      <c r="D16" s="245"/>
+      <c r="E16" s="248" t="s">
+        <v>112</v>
+      </c>
+      <c r="F16" s="249"/>
+      <c r="G16" s="85" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="25"/>
+      <c r="B17" s="26">
         <v>3</v>
       </c>
-      <c r="C17" s="232"/>
-      <c r="D17" s="233"/>
-      <c r="E17" s="126" t="s">
-        <v>90</v>
-      </c>
-      <c r="F17" s="127"/>
-    </row>
-    <row r="18" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A18" s="24"/>
-      <c r="B18" s="25">
+      <c r="C17" s="246"/>
+      <c r="D17" s="247"/>
+      <c r="E17" s="105" t="s">
+        <v>112</v>
+      </c>
+      <c r="F17" s="106"/>
+      <c r="G17" s="85" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A18" s="25"/>
+      <c r="B18" s="26">
         <v>4</v>
       </c>
-      <c r="C18" s="111" t="s">
-        <v>119</v>
-      </c>
-      <c r="D18" s="112"/>
-      <c r="E18" s="112"/>
-      <c r="F18" s="186"/>
-    </row>
-    <row r="19" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A19" s="24"/>
-      <c r="B19" s="25">
+      <c r="C18" s="161" t="s">
+        <v>149</v>
+      </c>
+      <c r="D18" s="162"/>
+      <c r="E18" s="162"/>
+      <c r="F18" s="224"/>
+      <c r="G18" s="85" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A19" s="25"/>
+      <c r="B19" s="26">
         <v>5</v>
       </c>
-      <c r="C19" s="111" t="s">
-        <v>120</v>
-      </c>
-      <c r="D19" s="112"/>
-      <c r="E19" s="112"/>
-      <c r="F19" s="186"/>
-    </row>
-    <row r="20" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="30"/>
-      <c r="B20" s="27">
+      <c r="C19" s="161" t="s">
+        <v>150</v>
+      </c>
+      <c r="D19" s="162"/>
+      <c r="E19" s="162"/>
+      <c r="F19" s="224"/>
+      <c r="G19" s="85" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="31"/>
+      <c r="B20" s="28">
         <v>6</v>
       </c>
-      <c r="C20" s="223"/>
-      <c r="D20" s="224"/>
-      <c r="E20" s="224"/>
-      <c r="F20" s="225"/>
-    </row>
-    <row r="21" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A21" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="29">
+      <c r="C20" s="237"/>
+      <c r="D20" s="238"/>
+      <c r="E20" s="238"/>
+      <c r="F20" s="239"/>
+      <c r="G20" s="83"/>
+    </row>
+    <row r="21" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A21" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="30">
         <v>2</v>
       </c>
-      <c r="C21" s="220"/>
-      <c r="D21" s="221"/>
-      <c r="E21" s="221"/>
-      <c r="F21" s="222"/>
-    </row>
-    <row r="22" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A22" s="24"/>
-      <c r="B22" s="25">
+      <c r="C21" s="234"/>
+      <c r="D21" s="235"/>
+      <c r="E21" s="235"/>
+      <c r="F21" s="236"/>
+      <c r="G21" s="46"/>
+    </row>
+    <row r="22" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A22" s="25"/>
+      <c r="B22" s="26">
         <v>3</v>
       </c>
-      <c r="C22" s="208"/>
-      <c r="D22" s="209"/>
-      <c r="E22" s="209"/>
-      <c r="F22" s="210"/>
-    </row>
-    <row r="23" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A23" s="24"/>
-      <c r="B23" s="25">
+      <c r="C22" s="256"/>
+      <c r="D22" s="257"/>
+      <c r="E22" s="257"/>
+      <c r="F22" s="258"/>
+      <c r="G22" s="46"/>
+    </row>
+    <row r="23" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A23" s="25"/>
+      <c r="B23" s="26">
         <v>4</v>
       </c>
-      <c r="C23" s="121" t="s">
-        <v>115</v>
-      </c>
-      <c r="D23" s="122"/>
-      <c r="E23" s="122"/>
-      <c r="F23" s="123"/>
-    </row>
-    <row r="24" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="30"/>
-      <c r="B24" s="27">
+      <c r="C23" s="96" t="s">
+        <v>145</v>
+      </c>
+      <c r="D23" s="97"/>
+      <c r="E23" s="97"/>
+      <c r="F23" s="98"/>
+      <c r="G23" s="79" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="31"/>
+      <c r="B24" s="28">
         <v>5</v>
       </c>
-      <c r="C24" s="73" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" s="74"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="75"/>
-    </row>
-    <row r="25" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A25" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" s="29">
+      <c r="C24" s="137" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="138"/>
+      <c r="E24" s="138"/>
+      <c r="F24" s="139"/>
+      <c r="G24" s="77" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A25" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="30">
         <v>1</v>
       </c>
-      <c r="C25" s="211" t="s">
-        <v>110</v>
-      </c>
-      <c r="D25" s="212"/>
-      <c r="E25" s="212"/>
-      <c r="F25" s="213"/>
-    </row>
-    <row r="26" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A26" s="24"/>
-      <c r="B26" s="25">
+      <c r="C25" s="259" t="s">
+        <v>140</v>
+      </c>
+      <c r="D25" s="260"/>
+      <c r="E25" s="260"/>
+      <c r="F25" s="261"/>
+      <c r="G25" s="80" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A26" s="25"/>
+      <c r="B26" s="26">
         <v>2</v>
       </c>
-      <c r="C26" s="211" t="s">
-        <v>110</v>
-      </c>
-      <c r="D26" s="212"/>
-      <c r="E26" s="212"/>
-      <c r="F26" s="213"/>
-    </row>
-    <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="24"/>
-      <c r="B27" s="25">
+      <c r="C26" s="259" t="s">
+        <v>140</v>
+      </c>
+      <c r="D26" s="260"/>
+      <c r="E26" s="260"/>
+      <c r="F26" s="261"/>
+      <c r="G26" s="79" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="25"/>
+      <c r="B27" s="26">
         <v>3</v>
       </c>
-      <c r="C27" s="70" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" s="71"/>
-      <c r="E27" s="71"/>
-      <c r="F27" s="72"/>
-    </row>
-    <row r="28" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="30"/>
-      <c r="B28" s="27">
+      <c r="C27" s="134" t="s">
+        <v>52</v>
+      </c>
+      <c r="D27" s="135"/>
+      <c r="E27" s="135"/>
+      <c r="F27" s="136"/>
+      <c r="G27" s="79" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="31"/>
+      <c r="B28" s="28">
         <v>4</v>
       </c>
-      <c r="C28" s="205" t="s">
-        <v>41</v>
-      </c>
-      <c r="D28" s="206"/>
-      <c r="E28" s="206"/>
-      <c r="F28" s="207"/>
-    </row>
-    <row r="29" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B29" s="29">
+      <c r="C28" s="262" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="263"/>
+      <c r="E28" s="263"/>
+      <c r="F28" s="264"/>
+      <c r="G28" s="77" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="30">
         <v>1</v>
       </c>
-      <c r="C29" s="165" t="s">
-        <v>107</v>
-      </c>
-      <c r="D29" s="166"/>
-      <c r="E29" s="166"/>
-      <c r="F29" s="167"/>
-    </row>
-    <row r="30" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="31"/>
-      <c r="B30" s="25">
+      <c r="C29" s="175" t="s">
+        <v>136</v>
+      </c>
+      <c r="D29" s="176"/>
+      <c r="E29" s="176"/>
+      <c r="F29" s="177"/>
+      <c r="G29" s="94" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="32"/>
+      <c r="B30" s="26">
         <v>2</v>
       </c>
-      <c r="C30" s="125" t="s">
-        <v>107</v>
-      </c>
-      <c r="D30" s="126"/>
-      <c r="E30" s="126"/>
-      <c r="F30" s="127"/>
-    </row>
-    <row r="31" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="31"/>
-      <c r="B31" s="25">
+      <c r="C30" s="104" t="s">
+        <v>136</v>
+      </c>
+      <c r="D30" s="105"/>
+      <c r="E30" s="105"/>
+      <c r="F30" s="106"/>
+      <c r="G30" s="85" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="32"/>
+      <c r="B31" s="26">
         <v>3</v>
       </c>
-      <c r="C31" s="79" t="s">
-        <v>108</v>
-      </c>
-      <c r="D31" s="80"/>
-      <c r="E31" s="80" t="s">
-        <v>109</v>
-      </c>
-      <c r="F31" s="81"/>
-    </row>
-    <row r="32" spans="1:6" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="32"/>
-      <c r="B32" s="27">
+      <c r="C31" s="103" t="s">
+        <v>138</v>
+      </c>
+      <c r="D31" s="101"/>
+      <c r="E31" s="101" t="s">
+        <v>139</v>
+      </c>
+      <c r="F31" s="102"/>
+      <c r="G31" s="85" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="33"/>
+      <c r="B32" s="28">
         <v>4</v>
       </c>
-      <c r="C32" s="217" t="s">
-        <v>108</v>
-      </c>
-      <c r="D32" s="218"/>
-      <c r="E32" s="218" t="s">
-        <v>109</v>
-      </c>
-      <c r="F32" s="219"/>
-    </row>
-    <row r="33" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A33" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="B33" s="23">
+      <c r="C32" s="253" t="s">
+        <v>138</v>
+      </c>
+      <c r="D32" s="254"/>
+      <c r="E32" s="254" t="s">
+        <v>139</v>
+      </c>
+      <c r="F32" s="255"/>
+      <c r="G32" s="86" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A33" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="B33" s="24">
         <v>1</v>
       </c>
-      <c r="C33" s="88" t="s">
-        <v>31</v>
-      </c>
-      <c r="D33" s="89"/>
-      <c r="E33" s="89"/>
-      <c r="F33" s="90"/>
-    </row>
-    <row r="34" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A34" s="34"/>
-      <c r="B34" s="25">
+      <c r="C33" s="146" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="147"/>
+      <c r="E33" s="147"/>
+      <c r="F33" s="148"/>
+      <c r="G33" s="62"/>
+    </row>
+    <row r="34" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A34" s="35"/>
+      <c r="B34" s="26">
         <v>2</v>
       </c>
-      <c r="C34" s="100"/>
-      <c r="D34" s="101"/>
-      <c r="E34" s="101"/>
-      <c r="F34" s="102"/>
-    </row>
-    <row r="35" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A35" s="34"/>
-      <c r="B35" s="25">
+      <c r="C34" s="155"/>
+      <c r="D34" s="156"/>
+      <c r="E34" s="156"/>
+      <c r="F34" s="157"/>
+      <c r="G34" s="46"/>
+    </row>
+    <row r="35" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A35" s="35"/>
+      <c r="B35" s="26">
         <v>3</v>
       </c>
-      <c r="C35" s="100"/>
-      <c r="D35" s="101"/>
-      <c r="E35" s="101"/>
-      <c r="F35" s="102"/>
-    </row>
-    <row r="36" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="38"/>
-      <c r="B36" s="54"/>
-      <c r="C36" s="214"/>
-      <c r="D36" s="215"/>
-      <c r="E36" s="215"/>
-      <c r="F36" s="216"/>
-    </row>
-    <row r="37" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="C35" s="155"/>
+      <c r="D35" s="156"/>
+      <c r="E35" s="156"/>
+      <c r="F35" s="157"/>
+      <c r="G35" s="46"/>
+    </row>
+    <row r="36" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="39"/>
+      <c r="B36" s="60"/>
+      <c r="C36" s="250"/>
+      <c r="D36" s="251"/>
+      <c r="E36" s="251"/>
+      <c r="F36" s="252"/>
+      <c r="G36" s="48"/>
+    </row>
+    <row r="37" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A37" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
-    </row>
-    <row r="38" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="G37" s="2"/>
+    </row>
+    <row r="38" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A38" s="2" t="s">
         <v>15</v>
       </c>
@@ -4092,25 +4586,45 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
-    </row>
-    <row r="39" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="G38" s="2"/>
+    </row>
+    <row r="39" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
-    </row>
-    <row r="40" spans="1:6" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="G39" s="2"/>
+    </row>
+    <row r="40" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="C33:F33"/>
     <mergeCell ref="C21:F21"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C11:F11"/>
@@ -4127,23 +4641,6 @@
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="E17:F17"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:E9">
     <cfRule type="expression" priority="2">
